--- a/streamlit_dashboard_monitoring/captured_data/with_ASCON/ppg_sensor_ascon_2.xlsx
+++ b/streamlit_dashboard_monitoring/captured_data/with_ASCON/ppg_sensor_ascon_2.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H155"/>
+  <dimension ref="A1:M158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,4625 +469,7095 @@
           <t>Sensor_Status</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>CPU_Load_%</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Memory_Used_%</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Latency_ms</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Enc_Time_us</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Dec_Time_ms</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-22 10:46:50.240</t>
+          <t>2026-05-29 09:33:52.902</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1779421611460</v>
+        <v>1780022030031</v>
       </c>
       <c r="C2" t="n">
-        <v>88634</v>
+        <v>75117</v>
       </c>
       <c r="D2" t="n">
-        <v>44.06</v>
+        <v>-5070.87</v>
       </c>
       <c r="E2" t="n">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="F2" t="n">
-        <v>604</v>
+        <v>2419</v>
       </c>
       <c r="G2" t="n">
-        <v>93.77</v>
+        <v>68.7</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I2" t="n">
+        <v>49.28</v>
+      </c>
+      <c r="J2" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K2" t="n">
+        <v>2869</v>
+      </c>
+      <c r="L2" t="n">
+        <v>103</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.445</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-22 10:46:50.241</t>
+          <t>2026-05-29 09:33:52.903</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1779421611661</v>
+        <v>1780022030231</v>
       </c>
       <c r="C3" t="n">
-        <v>88931</v>
+        <v>74647</v>
       </c>
       <c r="D3" t="n">
-        <v>338.86</v>
+        <v>-5287.33</v>
       </c>
       <c r="E3" t="n">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="F3" t="n">
-        <v>604</v>
+        <v>2419</v>
       </c>
       <c r="G3" t="n">
-        <v>93.77</v>
+        <v>68.7</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I3" t="n">
+        <v>49.28</v>
+      </c>
+      <c r="J3" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2671</v>
+      </c>
+      <c r="L3" t="n">
+        <v>106</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.899</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-22 10:46:50.242</t>
+          <t>2026-05-29 09:33:52.904</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1779421611863</v>
+        <v>1780022030431</v>
       </c>
       <c r="C4" t="n">
-        <v>89178</v>
+        <v>74456</v>
       </c>
       <c r="D4" t="n">
-        <v>568.91</v>
+        <v>-5213.96</v>
       </c>
       <c r="E4" t="n">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="F4" t="n">
-        <v>765</v>
+        <v>2419</v>
       </c>
       <c r="G4" t="n">
-        <v>89.20999999999999</v>
+        <v>68.7</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I4" t="n">
+        <v>49.28</v>
+      </c>
+      <c r="J4" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2472</v>
+      </c>
+      <c r="L4" t="n">
+        <v>107</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.004</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-22 10:46:50.244</t>
+          <t>2026-05-29 09:33:52.905</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1779421612064</v>
+        <v>1780022030650</v>
       </c>
       <c r="C5" t="n">
-        <v>89290</v>
+        <v>74528</v>
       </c>
       <c r="D5" t="n">
-        <v>652.47</v>
+        <v>-4881.26</v>
       </c>
       <c r="E5" t="n">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="F5" t="n">
-        <v>765</v>
+        <v>2419</v>
       </c>
       <c r="G5" t="n">
-        <v>89.20999999999999</v>
+        <v>68.7</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I5" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J5" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2254</v>
+      </c>
+      <c r="L5" t="n">
+        <v>107</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.876</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-22 10:46:50.244</t>
+          <t>2026-05-29 09:33:52.906</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1779421612266</v>
+        <v>1780022030850</v>
       </c>
       <c r="C6" t="n">
-        <v>88603</v>
+        <v>74455</v>
       </c>
       <c r="D6" t="n">
-        <v>-67.15000000000001</v>
+        <v>-4710.2</v>
       </c>
       <c r="E6" t="n">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="F6" t="n">
-        <v>765</v>
+        <v>2419</v>
       </c>
       <c r="G6" t="n">
-        <v>89.20999999999999</v>
+        <v>68.7</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I6" t="n">
+        <v>49.28</v>
+      </c>
+      <c r="J6" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2055</v>
+      </c>
+      <c r="L6" t="n">
+        <v>101</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.009</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-22 10:46:50.246</t>
+          <t>2026-05-29 09:33:52.907</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1779421612467</v>
+        <v>1780022031050</v>
       </c>
       <c r="C7" t="n">
-        <v>88777</v>
+        <v>74539</v>
       </c>
       <c r="D7" t="n">
-        <v>110.2</v>
+        <v>-4390.69</v>
       </c>
       <c r="E7" t="n">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="F7" t="n">
-        <v>765</v>
+        <v>2419</v>
       </c>
       <c r="G7" t="n">
-        <v>89.20999999999999</v>
+        <v>68.7</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I7" t="n">
+        <v>49.28</v>
+      </c>
+      <c r="J7" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1856</v>
+      </c>
+      <c r="L7" t="n">
+        <v>103</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.77</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-22 10:46:50.647</t>
+          <t>2026-05-29 09:33:52.909</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1779421612668</v>
+        <v>1780022031250</v>
       </c>
       <c r="C8" t="n">
-        <v>88837</v>
+        <v>75718</v>
       </c>
       <c r="D8" t="n">
-        <v>164.69</v>
+        <v>-2992.16</v>
       </c>
       <c r="E8" t="n">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="F8" t="n">
-        <v>765</v>
+        <v>3498</v>
       </c>
       <c r="G8" t="n">
-        <v>89.20999999999999</v>
+        <v>68.7</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I8" t="n">
+        <v>49.28</v>
+      </c>
+      <c r="J8" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1657</v>
+      </c>
+      <c r="L8" t="n">
+        <v>106</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.468</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-22 10:46:50.711</t>
+          <t>2026-05-29 09:33:52.911</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1779421612870</v>
+        <v>1780022031450</v>
       </c>
       <c r="C9" t="n">
-        <v>88384</v>
+        <v>75779</v>
       </c>
       <c r="D9" t="n">
-        <v>-296.54</v>
+        <v>-2781.55</v>
       </c>
       <c r="E9" t="n">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="F9" t="n">
-        <v>765</v>
+        <v>3498</v>
       </c>
       <c r="G9" t="n">
-        <v>89.20999999999999</v>
+        <v>68.7</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I9" t="n">
+        <v>49.28</v>
+      </c>
+      <c r="J9" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1460</v>
+      </c>
+      <c r="L9" t="n">
+        <v>105</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.837</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-22 10:46:51.053</t>
+          <t>2026-05-29 09:33:52.912</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1779421613071</v>
+        <v>1780022031650</v>
       </c>
       <c r="C10" t="n">
-        <v>88188</v>
+        <v>76312</v>
       </c>
       <c r="D10" t="n">
-        <v>-477.71</v>
+        <v>-2109.47</v>
       </c>
       <c r="E10" t="n">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="F10" t="n">
-        <v>765</v>
+        <v>3498</v>
       </c>
       <c r="G10" t="n">
-        <v>89.20999999999999</v>
+        <v>68.7</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I10" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J10" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1261</v>
+      </c>
+      <c r="L10" t="n">
+        <v>106</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.612</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-22 10:46:51.054</t>
+          <t>2026-05-29 09:33:52.912</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1779421613272</v>
+        <v>1780022031850</v>
       </c>
       <c r="C11" t="n">
-        <v>88231</v>
+        <v>77096</v>
       </c>
       <c r="D11" t="n">
-        <v>-410.83</v>
+        <v>-1220</v>
       </c>
       <c r="E11" t="n">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="F11" t="n">
-        <v>765</v>
+        <v>3498</v>
       </c>
       <c r="G11" t="n">
-        <v>89.20999999999999</v>
+        <v>68.7</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I11" t="n">
+        <v>49.28</v>
+      </c>
+      <c r="J11" t="n">
+        <v>34.98</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1062</v>
+      </c>
+      <c r="L11" t="n">
+        <v>107</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.596</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-22 10:46:51.443</t>
+          <t>2026-05-29 09:33:52.914</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1779421613474</v>
+        <v>1780022032050</v>
       </c>
       <c r="C12" t="n">
-        <v>88405</v>
+        <v>76905</v>
       </c>
       <c r="D12" t="n">
-        <v>-216.29</v>
+        <v>-1350</v>
       </c>
       <c r="E12" t="n">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="F12" t="n">
-        <v>765</v>
+        <v>3498</v>
       </c>
       <c r="G12" t="n">
-        <v>89.20999999999999</v>
+        <v>68.7</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I12" t="n">
+        <v>49.28</v>
+      </c>
+      <c r="J12" t="n">
+        <v>34.98</v>
+      </c>
+      <c r="K12" t="n">
+        <v>863</v>
+      </c>
+      <c r="L12" t="n">
+        <v>107</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.633</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-22 10:46:51.445</t>
+          <t>2026-05-29 09:33:53.252</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1779421613675</v>
+        <v>1780022032250</v>
       </c>
       <c r="C13" t="n">
-        <v>88034</v>
+        <v>77335</v>
       </c>
       <c r="D13" t="n">
-        <v>-576.47</v>
+        <v>-852.5</v>
       </c>
       <c r="E13" t="n">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="F13" t="n">
-        <v>1913</v>
+        <v>3498</v>
       </c>
       <c r="G13" t="n">
-        <v>89.20999999999999</v>
+        <v>68.7</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I13" t="n">
+        <v>49.28</v>
+      </c>
+      <c r="J13" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L13" t="n">
+        <v>106</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.593</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-05-22 10:46:51.960</t>
+          <t>2026-05-29 09:33:53.253</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1779421613876</v>
+        <v>1780022032450</v>
       </c>
       <c r="C14" t="n">
-        <v>88194</v>
+        <v>77789</v>
       </c>
       <c r="D14" t="n">
-        <v>-387.65</v>
+        <v>-355.87</v>
       </c>
       <c r="E14" t="n">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="F14" t="n">
-        <v>1913</v>
+        <v>3498</v>
       </c>
       <c r="G14" t="n">
-        <v>89.20999999999999</v>
+        <v>68.7</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I14" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J14" t="n">
+        <v>34.98</v>
+      </c>
+      <c r="K14" t="n">
+        <v>802</v>
+      </c>
+      <c r="L14" t="n">
+        <v>103</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.708</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-22 10:46:51.961</t>
+          <t>2026-05-29 09:33:53.837</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1779421614078</v>
+        <v>1780022032650</v>
       </c>
       <c r="C15" t="n">
-        <v>88418</v>
+        <v>77088</v>
       </c>
       <c r="D15" t="n">
-        <v>-144.27</v>
+        <v>-1039.08</v>
       </c>
       <c r="E15" t="n">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="F15" t="n">
-        <v>1913</v>
+        <v>3498</v>
       </c>
       <c r="G15" t="n">
-        <v>89.20999999999999</v>
+        <v>68.7</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I15" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J15" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1185</v>
+      </c>
+      <c r="L15" t="n">
+        <v>109</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.437</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-05-22 10:46:52.280</t>
+          <t>2026-05-29 09:33:53.838</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1779421614279</v>
+        <v>1780022032850</v>
       </c>
       <c r="C16" t="n">
-        <v>88573</v>
+        <v>77272</v>
       </c>
       <c r="D16" t="n">
-        <v>17.95</v>
+        <v>-803.12</v>
       </c>
       <c r="E16" t="n">
-        <v>95</v>
+        <v>66</v>
       </c>
       <c r="F16" t="n">
-        <v>463</v>
+        <v>3498</v>
       </c>
       <c r="G16" t="n">
-        <v>126.76</v>
+        <v>68.7</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I16" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J16" t="n">
+        <v>34.98</v>
+      </c>
+      <c r="K16" t="n">
+        <v>987</v>
+      </c>
+      <c r="L16" t="n">
+        <v>105</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.329</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-22 10:46:52.281</t>
+          <t>2026-05-29 09:33:54.357</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1779421614481</v>
+        <v>1780022033069</v>
       </c>
       <c r="C17" t="n">
-        <v>88064</v>
+        <v>77427</v>
       </c>
       <c r="D17" t="n">
-        <v>-491.95</v>
+        <v>-607.97</v>
       </c>
       <c r="E17" t="n">
-        <v>95</v>
+        <v>66</v>
       </c>
       <c r="F17" t="n">
-        <v>463</v>
+        <v>1859</v>
       </c>
       <c r="G17" t="n">
-        <v>126.76</v>
+        <v>68.7</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I17" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J17" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1287</v>
+      </c>
+      <c r="L17" t="n">
+        <v>106</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.215</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-05-22 10:46:52.679</t>
+          <t>2026-05-29 09:33:54.359</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1779421614682</v>
+        <v>1780022033269</v>
       </c>
       <c r="C18" t="n">
-        <v>88283</v>
+        <v>77491</v>
       </c>
       <c r="D18" t="n">
-        <v>-248.35</v>
+        <v>-513.5700000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>95</v>
+        <v>66</v>
       </c>
       <c r="F18" t="n">
-        <v>463</v>
+        <v>1859</v>
       </c>
       <c r="G18" t="n">
-        <v>126.76</v>
+        <v>68.7</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I18" t="n">
+        <v>49.28</v>
+      </c>
+      <c r="J18" t="n">
+        <v>34.98</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1089</v>
+      </c>
+      <c r="L18" t="n">
+        <v>106</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.637</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-22 10:46:52.680</t>
+          <t>2026-05-29 09:33:55.438</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1779421614883</v>
+        <v>1780022033469</v>
       </c>
       <c r="C19" t="n">
-        <v>88523</v>
+        <v>77197</v>
       </c>
       <c r="D19" t="n">
-        <v>4.06</v>
+        <v>-781.89</v>
       </c>
       <c r="E19" t="n">
-        <v>97</v>
+        <v>66</v>
       </c>
       <c r="F19" t="n">
-        <v>725</v>
+        <v>1859</v>
       </c>
       <c r="G19" t="n">
-        <v>125.63</v>
+        <v>68.7</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I19" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J19" t="n">
+        <v>34.49</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1968</v>
+      </c>
+      <c r="L19" t="n">
+        <v>107</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.991</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-05-22 10:46:53.091</t>
+          <t>2026-05-29 09:33:55.448</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1779421615085</v>
+        <v>1780022033669</v>
       </c>
       <c r="C20" t="n">
-        <v>88257</v>
+        <v>76707</v>
       </c>
       <c r="D20" t="n">
-        <v>-262.14</v>
+        <v>-1232.8</v>
       </c>
       <c r="E20" t="n">
-        <v>97</v>
+        <v>66</v>
       </c>
       <c r="F20" t="n">
-        <v>725</v>
+        <v>1859</v>
       </c>
       <c r="G20" t="n">
-        <v>125.63</v>
+        <v>68.7</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I20" t="n">
+        <v>49.28</v>
+      </c>
+      <c r="J20" t="n">
+        <v>34.98</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1778</v>
+      </c>
+      <c r="L20" t="n">
+        <v>107</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.67</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-22 10:46:53.092</t>
+          <t>2026-05-29 09:33:55.449</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1779421615286</v>
+        <v>1780022033869</v>
       </c>
       <c r="C21" t="n">
-        <v>88205</v>
+        <v>76517</v>
       </c>
       <c r="D21" t="n">
-        <v>-301.03</v>
+        <v>-1361.16</v>
       </c>
       <c r="E21" t="n">
-        <v>97</v>
+        <v>66</v>
       </c>
       <c r="F21" t="n">
-        <v>725</v>
+        <v>1859</v>
       </c>
       <c r="G21" t="n">
-        <v>125.63</v>
+        <v>68.7</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I21" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J21" t="n">
+        <v>34.98</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1579</v>
+      </c>
+      <c r="L21" t="n">
+        <v>119</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.504</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-05-22 10:46:53.506</t>
+          <t>2026-05-29 09:33:55.810</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1779421615487</v>
+        <v>1780022034069</v>
       </c>
       <c r="C22" t="n">
-        <v>88409</v>
+        <v>75839</v>
       </c>
       <c r="D22" t="n">
-        <v>-81.98</v>
+        <v>-1971.1</v>
       </c>
       <c r="E22" t="n">
-        <v>97</v>
+        <v>66</v>
       </c>
       <c r="F22" t="n">
-        <v>725</v>
+        <v>1859</v>
       </c>
       <c r="G22" t="n">
-        <v>125.63</v>
+        <v>68.7</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I22" t="n">
+        <v>49.28</v>
+      </c>
+      <c r="J22" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1740</v>
+      </c>
+      <c r="L22" t="n">
+        <v>106</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.975</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-22 10:46:53.507</t>
+          <t>2026-05-29 09:33:55.812</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1779421615689</v>
+        <v>1780022034269</v>
       </c>
       <c r="C23" t="n">
-        <v>88676</v>
+        <v>75718</v>
       </c>
       <c r="D23" t="n">
-        <v>189.12</v>
+        <v>-1993.54</v>
       </c>
       <c r="E23" t="n">
-        <v>91</v>
+        <v>66</v>
       </c>
       <c r="F23" t="n">
-        <v>765</v>
+        <v>1859</v>
       </c>
       <c r="G23" t="n">
-        <v>108.1</v>
+        <v>68.7</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I23" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J23" t="n">
+        <v>34.98</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1541</v>
+      </c>
+      <c r="L23" t="n">
+        <v>105</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.783</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-05-22 10:46:54.031</t>
+          <t>2026-05-29 09:33:55.815</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1779421615890</v>
+        <v>1780022034469</v>
       </c>
       <c r="C24" t="n">
-        <v>88143</v>
+        <v>76141</v>
       </c>
       <c r="D24" t="n">
-        <v>-353.34</v>
+        <v>-1470.87</v>
       </c>
       <c r="E24" t="n">
-        <v>91</v>
+        <v>66</v>
       </c>
       <c r="F24" t="n">
-        <v>765</v>
+        <v>1859</v>
       </c>
       <c r="G24" t="n">
-        <v>108.1</v>
+        <v>68.7</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I24" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J24" t="n">
+        <v>34.98</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1343</v>
+      </c>
+      <c r="L24" t="n">
+        <v>104</v>
+      </c>
+      <c r="M24" t="n">
+        <v>2.417</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-05-22 10:46:54.032</t>
+          <t>2026-05-29 09:33:55.817</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1779421616092</v>
+        <v>1780022034669</v>
       </c>
       <c r="C25" t="n">
-        <v>88342</v>
+        <v>76125</v>
       </c>
       <c r="D25" t="n">
-        <v>-136.67</v>
+        <v>-1413.32</v>
       </c>
       <c r="E25" t="n">
-        <v>91</v>
+        <v>66</v>
       </c>
       <c r="F25" t="n">
-        <v>765</v>
+        <v>1859</v>
       </c>
       <c r="G25" t="n">
-        <v>108.1</v>
+        <v>68.7</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I25" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J25" t="n">
+        <v>34.98</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1146</v>
+      </c>
+      <c r="L25" t="n">
+        <v>107</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.597</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-05-22 10:46:54.331</t>
+          <t>2026-05-29 09:33:56.340</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1779421616293</v>
+        <v>1780022034869</v>
       </c>
       <c r="C26" t="n">
-        <v>88503</v>
+        <v>76059</v>
       </c>
       <c r="D26" t="n">
-        <v>31.16</v>
+        <v>-1408.66</v>
       </c>
       <c r="E26" t="n">
-        <v>91</v>
+        <v>66</v>
       </c>
       <c r="F26" t="n">
-        <v>765</v>
+        <v>1859</v>
       </c>
       <c r="G26" t="n">
-        <v>108.1</v>
+        <v>68.7</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I26" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J26" t="n">
+        <v>34.98</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1470</v>
+      </c>
+      <c r="L26" t="n">
+        <v>103</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.02</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-05-22 10:46:54.332</t>
+          <t>2026-05-29 09:33:56.341</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1779421616494</v>
+        <v>1780022035069</v>
       </c>
       <c r="C27" t="n">
-        <v>88679</v>
+        <v>76376</v>
       </c>
       <c r="D27" t="n">
-        <v>205.61</v>
+        <v>-1021.22</v>
       </c>
       <c r="E27" t="n">
-        <v>91</v>
+        <v>66</v>
       </c>
       <c r="F27" t="n">
-        <v>766</v>
+        <v>1859</v>
       </c>
       <c r="G27" t="n">
-        <v>108.78</v>
+        <v>68.7</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I27" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J27" t="n">
+        <v>35.47</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1271</v>
+      </c>
+      <c r="L27" t="n">
+        <v>107</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.256</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-05-22 10:46:54.730</t>
+          <t>2026-05-29 09:33:56.343</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1779421616696</v>
+        <v>1780022035288</v>
       </c>
       <c r="C28" t="n">
-        <v>88200</v>
+        <v>75813</v>
       </c>
       <c r="D28" t="n">
-        <v>-283.68</v>
+        <v>-1533.16</v>
       </c>
       <c r="E28" t="n">
-        <v>91</v>
+        <v>66</v>
       </c>
       <c r="F28" t="n">
-        <v>766</v>
+        <v>2059</v>
       </c>
       <c r="G28" t="n">
-        <v>108.78</v>
+        <v>68.7</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I28" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J28" t="n">
+        <v>34.49</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1054</v>
+      </c>
+      <c r="L28" t="n">
+        <v>114</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.339</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-05-22 10:46:54.731</t>
+          <t>2026-05-29 09:33:56.351</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1779421616897</v>
+        <v>1780022035488</v>
       </c>
       <c r="C29" t="n">
-        <v>88556</v>
+        <v>75938</v>
       </c>
       <c r="D29" t="n">
-        <v>86.51000000000001</v>
+        <v>-1331.51</v>
       </c>
       <c r="E29" t="n">
-        <v>91</v>
+        <v>66</v>
       </c>
       <c r="F29" t="n">
-        <v>766</v>
+        <v>2059</v>
       </c>
       <c r="G29" t="n">
-        <v>108.78</v>
+        <v>68.7</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I29" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J29" t="n">
+        <v>34.98</v>
+      </c>
+      <c r="K29" t="n">
+        <v>862</v>
+      </c>
+      <c r="L29" t="n">
+        <v>105</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.717</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-05-22 10:46:55.136</t>
+          <t>2026-05-29 09:33:57.096</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1779421617099</v>
+        <v>1780022035688</v>
       </c>
       <c r="C30" t="n">
-        <v>88969</v>
+        <v>75883</v>
       </c>
       <c r="D30" t="n">
-        <v>495.18</v>
+        <v>-1319.93</v>
       </c>
       <c r="E30" t="n">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="F30" t="n">
-        <v>644</v>
+        <v>2059</v>
       </c>
       <c r="G30" t="n">
-        <v>107.43</v>
+        <v>68.7</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I30" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J30" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1407</v>
+      </c>
+      <c r="L30" t="n">
+        <v>106</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.909</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-05-22 10:46:55.138</t>
+          <t>2026-05-29 09:33:57.113</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1779421617300</v>
+        <v>1780022035888</v>
       </c>
       <c r="C31" t="n">
-        <v>88522</v>
+        <v>76092</v>
       </c>
       <c r="D31" t="n">
-        <v>23.42</v>
+        <v>-1044.93</v>
       </c>
       <c r="E31" t="n">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="F31" t="n">
-        <v>644</v>
+        <v>2059</v>
       </c>
       <c r="G31" t="n">
-        <v>107.43</v>
+        <v>68.7</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I31" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J31" t="n">
+        <v>34.98</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1224</v>
+      </c>
+      <c r="L31" t="n">
+        <v>105</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.515</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-05-22 10:46:55.632</t>
+          <t>2026-05-29 09:33:57.120</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1779421617501</v>
+        <v>1780022036088</v>
       </c>
       <c r="C32" t="n">
-        <v>88669</v>
+        <v>75463</v>
       </c>
       <c r="D32" t="n">
-        <v>169.25</v>
+        <v>-1621.69</v>
       </c>
       <c r="E32" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F32" t="n">
-        <v>644</v>
+        <v>840</v>
       </c>
       <c r="G32" t="n">
-        <v>107.43</v>
+        <v>97.84</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I32" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J32" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1031</v>
+      </c>
+      <c r="L32" t="n">
+        <v>105</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.977</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-22 10:46:55.633</t>
+          <t>2026-05-29 09:33:58.793</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1779421617703</v>
+        <v>1780022036288</v>
       </c>
       <c r="C33" t="n">
-        <v>88873</v>
+        <v>75104</v>
       </c>
       <c r="D33" t="n">
-        <v>364.79</v>
+        <v>-1899.6</v>
       </c>
       <c r="E33" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F33" t="n">
-        <v>644</v>
+        <v>840</v>
       </c>
       <c r="G33" t="n">
-        <v>107.43</v>
+        <v>97.84</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I33" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J33" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K33" t="n">
+        <v>2504</v>
+      </c>
+      <c r="L33" t="n">
+        <v>109</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1.077</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-05-22 10:46:55.869</t>
+          <t>2026-05-29 09:33:58.795</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1779421617904</v>
+        <v>1780022036488</v>
       </c>
       <c r="C34" t="n">
-        <v>89186</v>
+        <v>75158</v>
       </c>
       <c r="D34" t="n">
-        <v>659.55</v>
+        <v>-1750.62</v>
       </c>
       <c r="E34" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F34" t="n">
-        <v>745</v>
+        <v>840</v>
       </c>
       <c r="G34" t="n">
-        <v>106.45</v>
+        <v>97.84</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I34" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J34" t="n">
+        <v>34.98</v>
+      </c>
+      <c r="K34" t="n">
+        <v>2306</v>
+      </c>
+      <c r="L34" t="n">
+        <v>107</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1.155</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-22 10:46:55.877</t>
+          <t>2026-05-29 09:33:58.796</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1779421618105</v>
+        <v>1780022036688</v>
       </c>
       <c r="C35" t="n">
-        <v>88476</v>
+        <v>74805</v>
       </c>
       <c r="D35" t="n">
-        <v>-83.43000000000001</v>
+        <v>-2016.09</v>
       </c>
       <c r="E35" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F35" t="n">
-        <v>745</v>
+        <v>840</v>
       </c>
       <c r="G35" t="n">
-        <v>106.45</v>
+        <v>97.84</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I35" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J35" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="K35" t="n">
+        <v>2107</v>
+      </c>
+      <c r="L35" t="n">
+        <v>106</v>
+      </c>
+      <c r="M35" t="n">
+        <v>1.067</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-22 10:46:56.157</t>
+          <t>2026-05-29 09:33:58.797</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1779421618307</v>
+        <v>1780022036888</v>
       </c>
       <c r="C36" t="n">
-        <v>88246</v>
+        <v>75036</v>
       </c>
       <c r="D36" t="n">
-        <v>-309.26</v>
+        <v>-1684.29</v>
       </c>
       <c r="E36" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F36" t="n">
-        <v>745</v>
+        <v>840</v>
       </c>
       <c r="G36" t="n">
-        <v>106.45</v>
+        <v>97.84</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I36" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J36" t="n">
+        <v>34.98</v>
+      </c>
+      <c r="K36" t="n">
+        <v>1908</v>
+      </c>
+      <c r="L36" t="n">
+        <v>107</v>
+      </c>
+      <c r="M36" t="n">
+        <v>1.078</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-22 10:46:56.576</t>
+          <t>2026-05-29 09:33:58.799</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1779421618508</v>
+        <v>1780022037088</v>
       </c>
       <c r="C37" t="n">
-        <v>88882</v>
+        <v>75030</v>
       </c>
       <c r="D37" t="n">
-        <v>342.21</v>
+        <v>-1606.07</v>
       </c>
       <c r="E37" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F37" t="n">
-        <v>745</v>
+        <v>840</v>
       </c>
       <c r="G37" t="n">
-        <v>106.45</v>
+        <v>97.84</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I37" t="n">
+        <v>49.27</v>
+      </c>
+      <c r="J37" t="n">
+        <v>35</v>
+      </c>
+      <c r="K37" t="n">
+        <v>1710</v>
+      </c>
+      <c r="L37" t="n">
+        <v>113</v>
+      </c>
+      <c r="M37" t="n">
+        <v>1.073</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-22 10:46:56.627</t>
+          <t>2026-05-29 09:33:58.800</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1779421618710</v>
+        <v>1780022037307</v>
       </c>
       <c r="C38" t="n">
-        <v>89102</v>
+        <v>74680</v>
       </c>
       <c r="D38" t="n">
-        <v>545.1</v>
+        <v>-1875.77</v>
       </c>
       <c r="E38" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="F38" t="n">
-        <v>886</v>
+        <v>1200</v>
       </c>
       <c r="G38" t="n">
-        <v>118.77</v>
+        <v>230.89</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I38" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J38" t="n">
+        <v>34.98</v>
+      </c>
+      <c r="K38" t="n">
+        <v>1492</v>
+      </c>
+      <c r="L38" t="n">
+        <v>106</v>
+      </c>
+      <c r="M38" t="n">
+        <v>1.095</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-22 10:46:56.967</t>
+          <t>2026-05-29 09:33:58.802</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1779421618911</v>
+        <v>1780022037507</v>
       </c>
       <c r="C39" t="n">
-        <v>88473</v>
+        <v>75249</v>
       </c>
       <c r="D39" t="n">
-        <v>-111.16</v>
+        <v>-1212.98</v>
       </c>
       <c r="E39" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="F39" t="n">
-        <v>886</v>
+        <v>1200</v>
       </c>
       <c r="G39" t="n">
-        <v>118.77</v>
+        <v>230.89</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I39" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J39" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="K39" t="n">
+        <v>1293</v>
+      </c>
+      <c r="L39" t="n">
+        <v>109</v>
+      </c>
+      <c r="M39" t="n">
+        <v>1.708</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-22 10:46:56.967</t>
+          <t>2026-05-29 09:33:59.009</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1779421619112</v>
+        <v>1780022037707</v>
       </c>
       <c r="C40" t="n">
-        <v>88625</v>
+        <v>75812</v>
       </c>
       <c r="D40" t="n">
-        <v>46.4</v>
+        <v>-589.33</v>
       </c>
       <c r="E40" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="F40" t="n">
-        <v>886</v>
+        <v>479</v>
       </c>
       <c r="G40" t="n">
-        <v>118.77</v>
+        <v>248.1</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I40" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J40" t="n">
+        <v>34.98</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1301</v>
+      </c>
+      <c r="L40" t="n">
+        <v>106</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0.966</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-22 10:46:57.408</t>
+          <t>2026-05-29 09:33:59.010</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1779421619314</v>
+        <v>1780022037907</v>
       </c>
       <c r="C41" t="n">
-        <v>88737</v>
+        <v>75681</v>
       </c>
       <c r="D41" t="n">
-        <v>156.08</v>
+        <v>-690.86</v>
       </c>
       <c r="E41" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="F41" t="n">
-        <v>886</v>
+        <v>479</v>
       </c>
       <c r="G41" t="n">
-        <v>118.77</v>
+        <v>248.1</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I41" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J41" t="n">
+        <v>34.98</v>
+      </c>
+      <c r="K41" t="n">
+        <v>1102</v>
+      </c>
+      <c r="L41" t="n">
+        <v>104</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0.822</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-05-22 10:46:57.415</t>
+          <t>2026-05-29 09:33:59.161</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1779421619515</v>
+        <v>1780022038107</v>
       </c>
       <c r="C42" t="n">
-        <v>88249</v>
+        <v>75232</v>
       </c>
       <c r="D42" t="n">
-        <v>-339.72</v>
+        <v>-1105.32</v>
       </c>
       <c r="E42" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="F42" t="n">
-        <v>765</v>
+        <v>479</v>
       </c>
       <c r="G42" t="n">
-        <v>116.03</v>
+        <v>248.1</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I42" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J42" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="K42" t="n">
+        <v>1053</v>
+      </c>
+      <c r="L42" t="n">
+        <v>107</v>
+      </c>
+      <c r="M42" t="n">
+        <v>1.176</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-05-22 10:46:57.891</t>
+          <t>2026-05-29 09:33:59.163</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1779421619716</v>
+        <v>1780022038307</v>
       </c>
       <c r="C43" t="n">
-        <v>87812</v>
+        <v>75561</v>
       </c>
       <c r="D43" t="n">
-        <v>-759.74</v>
+        <v>-721.0599999999999</v>
       </c>
       <c r="E43" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="F43" t="n">
-        <v>765</v>
+        <v>479</v>
       </c>
       <c r="G43" t="n">
-        <v>116.03</v>
+        <v>248.1</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I43" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J43" t="n">
+        <v>34.98</v>
+      </c>
+      <c r="K43" t="n">
+        <v>855</v>
+      </c>
+      <c r="L43" t="n">
+        <v>106</v>
+      </c>
+      <c r="M43" t="n">
+        <v>1.463</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-05-22 10:46:57.892</t>
+          <t>2026-05-29 09:33:59.572</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1779421619918</v>
+        <v>1780022038507</v>
       </c>
       <c r="C44" t="n">
-        <v>87783</v>
+        <v>76010</v>
       </c>
       <c r="D44" t="n">
-        <v>-750.75</v>
+        <v>-236</v>
       </c>
       <c r="E44" t="n">
         <v>79</v>
       </c>
       <c r="F44" t="n">
-        <v>765</v>
+        <v>820</v>
       </c>
       <c r="G44" t="n">
-        <v>116.03</v>
+        <v>227.63</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I44" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J44" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K44" t="n">
+        <v>1064</v>
+      </c>
+      <c r="L44" t="n">
+        <v>107</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0.921</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-05-22 10:46:58.221</t>
+          <t>2026-05-29 09:33:59.573</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1779421620119</v>
+        <v>1780022038707</v>
       </c>
       <c r="C45" t="n">
-        <v>87899</v>
+        <v>75720</v>
       </c>
       <c r="D45" t="n">
-        <v>-597.21</v>
+        <v>-514.2</v>
       </c>
       <c r="E45" t="n">
         <v>79</v>
       </c>
       <c r="F45" t="n">
-        <v>765</v>
+        <v>820</v>
       </c>
       <c r="G45" t="n">
-        <v>116.03</v>
+        <v>227.63</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I45" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J45" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K45" t="n">
+        <v>865</v>
+      </c>
+      <c r="L45" t="n">
+        <v>112</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0.6929999999999999</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-05-22 10:46:58.249</t>
+          <t>2026-05-29 09:34:00.677</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1779421620321</v>
+        <v>1780022038907</v>
       </c>
       <c r="C46" t="n">
-        <v>87304</v>
+        <v>75717</v>
       </c>
       <c r="D46" t="n">
-        <v>-1162.35</v>
+        <v>-491.49</v>
       </c>
       <c r="E46" t="n">
         <v>79</v>
       </c>
       <c r="F46" t="n">
-        <v>765</v>
+        <v>820</v>
       </c>
       <c r="G46" t="n">
-        <v>116.03</v>
+        <v>227.63</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I46" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J46" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K46" t="n">
+        <v>1770</v>
+      </c>
+      <c r="L46" t="n">
+        <v>106</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0.8129999999999999</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-05-22 10:46:58.622</t>
+          <t>2026-05-29 09:34:00.679</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1779421620522</v>
+        <v>1780022039107</v>
       </c>
       <c r="C47" t="n">
-        <v>87490</v>
+        <v>75522</v>
       </c>
       <c r="D47" t="n">
-        <v>-918.24</v>
+        <v>-661.92</v>
       </c>
       <c r="E47" t="n">
         <v>79</v>
       </c>
       <c r="F47" t="n">
-        <v>765</v>
+        <v>820</v>
       </c>
       <c r="G47" t="n">
-        <v>116.03</v>
+        <v>227.63</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I47" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J47" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K47" t="n">
+        <v>1571</v>
+      </c>
+      <c r="L47" t="n">
+        <v>105</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0.878</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-05-22 10:46:58.647</t>
+          <t>2026-05-29 09:34:00.679</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1779421620723</v>
+        <v>1780022039326</v>
       </c>
       <c r="C48" t="n">
-        <v>87717</v>
+        <v>76099</v>
       </c>
       <c r="D48" t="n">
-        <v>-645.3200000000001</v>
+        <v>-51.82</v>
       </c>
       <c r="E48" t="n">
         <v>79</v>
       </c>
       <c r="F48" t="n">
-        <v>765</v>
+        <v>820</v>
       </c>
       <c r="G48" t="n">
-        <v>116.03</v>
+        <v>227.63</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I48" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J48" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K48" t="n">
+        <v>1353</v>
+      </c>
+      <c r="L48" t="n">
+        <v>103</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0.513</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-05-22 10:46:59.042</t>
+          <t>2026-05-29 09:34:00.680</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1779421620925</v>
+        <v>1780022039526</v>
       </c>
       <c r="C49" t="n">
-        <v>88003</v>
+        <v>76590</v>
       </c>
       <c r="D49" t="n">
-        <v>-327.06</v>
+        <v>441.77</v>
       </c>
       <c r="E49" t="n">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="F49" t="n">
-        <v>1450</v>
+        <v>979</v>
       </c>
       <c r="G49" t="n">
-        <v>254.12</v>
+        <v>223.52</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I49" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J49" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K49" t="n">
+        <v>1153</v>
+      </c>
+      <c r="L49" t="n">
+        <v>104</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0.498</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-05-22 10:46:59.043</t>
+          <t>2026-05-29 09:34:01.391</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1779421621126</v>
+        <v>1780022039726</v>
       </c>
       <c r="C50" t="n">
-        <v>88008</v>
+        <v>76304</v>
       </c>
       <c r="D50" t="n">
-        <v>-305.7</v>
+        <v>133.68</v>
       </c>
       <c r="E50" t="n">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="F50" t="n">
-        <v>1450</v>
+        <v>979</v>
       </c>
       <c r="G50" t="n">
-        <v>254.12</v>
+        <v>223.52</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I50" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J50" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K50" t="n">
+        <v>1664</v>
+      </c>
+      <c r="L50" t="n">
+        <v>106</v>
+      </c>
+      <c r="M50" t="n">
+        <v>1.206</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-05-22 10:46:59.465</t>
+          <t>2026-05-29 09:34:01.394</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1779421621328</v>
+        <v>1780022039926</v>
       </c>
       <c r="C51" t="n">
-        <v>87663</v>
+        <v>76711</v>
       </c>
       <c r="D51" t="n">
-        <v>-635.42</v>
+        <v>534</v>
       </c>
       <c r="E51" t="n">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="F51" t="n">
-        <v>1450</v>
+        <v>979</v>
       </c>
       <c r="G51" t="n">
-        <v>254.12</v>
+        <v>223.52</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I51" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J51" t="n">
+        <v>35.46</v>
+      </c>
+      <c r="K51" t="n">
+        <v>1466</v>
+      </c>
+      <c r="L51" t="n">
+        <v>108</v>
+      </c>
+      <c r="M51" t="n">
+        <v>1.392</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-05-22 10:46:59.469</t>
+          <t>2026-05-29 09:34:01.395</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1779421621529</v>
+        <v>1780022040126</v>
       </c>
       <c r="C52" t="n">
-        <v>87897</v>
+        <v>76824</v>
       </c>
       <c r="D52" t="n">
-        <v>-369.65</v>
+        <v>620.3</v>
       </c>
       <c r="E52" t="n">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="F52" t="n">
-        <v>1450</v>
+        <v>979</v>
       </c>
       <c r="G52" t="n">
-        <v>254.12</v>
+        <v>223.52</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I52" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J52" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K52" t="n">
+        <v>1268</v>
+      </c>
+      <c r="L52" t="n">
+        <v>107</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0.92</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-05-22 10:46:59.846</t>
+          <t>2026-05-29 09:34:01.842</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1779421621730</v>
+        <v>1780022040326</v>
       </c>
       <c r="C53" t="n">
-        <v>88150</v>
+        <v>77393</v>
       </c>
       <c r="D53" t="n">
-        <v>-98.17</v>
+        <v>1158.28</v>
       </c>
       <c r="E53" t="n">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="F53" t="n">
-        <v>806</v>
+        <v>979</v>
       </c>
       <c r="G53" t="n">
-        <v>253.87</v>
+        <v>223.52</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I53" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J53" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K53" t="n">
+        <v>1515</v>
+      </c>
+      <c r="L53" t="n">
+        <v>109</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0.705</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-05-22 10:46:59.847</t>
+          <t>2026-05-29 09:34:01.843</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1779421621932</v>
+        <v>1780022040526</v>
       </c>
       <c r="C54" t="n">
-        <v>88304</v>
+        <v>77274</v>
       </c>
       <c r="D54" t="n">
-        <v>60.74</v>
+        <v>981.37</v>
       </c>
       <c r="E54" t="n">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="F54" t="n">
-        <v>806</v>
+        <v>979</v>
       </c>
       <c r="G54" t="n">
-        <v>253.87</v>
+        <v>223.52</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I54" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J54" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K54" t="n">
+        <v>1316</v>
+      </c>
+      <c r="L54" t="n">
+        <v>105</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0.6879999999999999</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:00.275</t>
+          <t>2026-05-29 09:34:01.845</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>1779421622133</v>
+        <v>1780022040726</v>
       </c>
       <c r="C55" t="n">
-        <v>87656</v>
+        <v>77291</v>
       </c>
       <c r="D55" t="n">
-        <v>-590.29</v>
+        <v>949.3</v>
       </c>
       <c r="E55" t="n">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="F55" t="n">
-        <v>806</v>
+        <v>979</v>
       </c>
       <c r="G55" t="n">
-        <v>253.87</v>
+        <v>223.52</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I55" t="n">
+        <v>49.28</v>
+      </c>
+      <c r="J55" t="n">
+        <v>34.98</v>
+      </c>
+      <c r="K55" t="n">
+        <v>1117</v>
+      </c>
+      <c r="L55" t="n">
+        <v>105</v>
+      </c>
+      <c r="M55" t="n">
+        <v>1.81</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:00.276</t>
+          <t>2026-05-29 09:34:01.846</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>1779421622335</v>
+        <v>1780022040926</v>
       </c>
       <c r="C56" t="n">
-        <v>87785</v>
+        <v>77548</v>
       </c>
       <c r="D56" t="n">
-        <v>-431.78</v>
+        <v>1158.83</v>
       </c>
       <c r="E56" t="n">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="F56" t="n">
-        <v>806</v>
+        <v>979</v>
       </c>
       <c r="G56" t="n">
-        <v>253.87</v>
+        <v>223.52</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I56" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J56" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K56" t="n">
+        <v>919</v>
+      </c>
+      <c r="L56" t="n">
+        <v>101</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0.697</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:00.683</t>
+          <t>2026-05-29 09:34:02.679</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>1779421622536</v>
+        <v>1780022041126</v>
       </c>
       <c r="C57" t="n">
-        <v>87886</v>
+        <v>77476</v>
       </c>
       <c r="D57" t="n">
-        <v>-309.19</v>
+        <v>1028.89</v>
       </c>
       <c r="E57" t="n">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="F57" t="n">
-        <v>806</v>
+        <v>979</v>
       </c>
       <c r="G57" t="n">
-        <v>253.87</v>
+        <v>223.52</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I57" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J57" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K57" t="n">
+        <v>1552</v>
+      </c>
+      <c r="L57" t="n">
+        <v>115</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0.744</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:00.700</t>
+          <t>2026-05-29 09:34:02.679</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>1779421622737</v>
+        <v>1780022041326</v>
       </c>
       <c r="C58" t="n">
-        <v>87997</v>
+        <v>77660</v>
       </c>
       <c r="D58" t="n">
-        <v>-182.73</v>
+        <v>1161.45</v>
       </c>
       <c r="E58" t="n">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="F58" t="n">
-        <v>1007</v>
+        <v>979</v>
       </c>
       <c r="G58" t="n">
-        <v>230.49</v>
+        <v>223.52</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I58" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J58" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K58" t="n">
+        <v>1353</v>
+      </c>
+      <c r="L58" t="n">
+        <v>104</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0.609</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:01.222</t>
+          <t>2026-05-29 09:34:03.668</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>1779421622939</v>
+        <v>1780022041545</v>
       </c>
       <c r="C59" t="n">
-        <v>87527</v>
+        <v>78988</v>
       </c>
       <c r="D59" t="n">
-        <v>-643.59</v>
+        <v>2431.38</v>
       </c>
       <c r="E59" t="n">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="F59" t="n">
-        <v>1007</v>
+        <v>979</v>
       </c>
       <c r="G59" t="n">
-        <v>230.49</v>
+        <v>223.52</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I59" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J59" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K59" t="n">
+        <v>2122</v>
+      </c>
+      <c r="L59" t="n">
+        <v>105</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0.946</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:01.223</t>
+          <t>2026-05-29 09:34:03.712</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>1779421623140</v>
+        <v>1780022041745</v>
       </c>
       <c r="C60" t="n">
-        <v>87706</v>
+        <v>79656</v>
       </c>
       <c r="D60" t="n">
-        <v>-432.42</v>
+        <v>2977.81</v>
       </c>
       <c r="E60" t="n">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="F60" t="n">
-        <v>1007</v>
+        <v>979</v>
       </c>
       <c r="G60" t="n">
-        <v>230.49</v>
+        <v>223.52</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I60" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J60" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K60" t="n">
+        <v>1966</v>
+      </c>
+      <c r="L60" t="n">
+        <v>106</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0.88</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:01.224</t>
+          <t>2026-05-29 09:34:03.713</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>1779421623342</v>
+        <v>1780022041945</v>
       </c>
       <c r="C61" t="n">
-        <v>87916</v>
+        <v>78327</v>
       </c>
       <c r="D61" t="n">
-        <v>-200.79</v>
+        <v>1499.92</v>
       </c>
       <c r="E61" t="n">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="F61" t="n">
-        <v>665</v>
+        <v>979</v>
       </c>
       <c r="G61" t="n">
-        <v>235.01</v>
+        <v>223.52</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I61" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J61" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K61" t="n">
+        <v>1767</v>
+      </c>
+      <c r="L61" t="n">
+        <v>104</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0.874</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:01.586</t>
+          <t>2026-05-29 09:34:03.744</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>1779421623543</v>
+        <v>1780022042145</v>
       </c>
       <c r="C62" t="n">
-        <v>88132</v>
+        <v>77340</v>
       </c>
       <c r="D62" t="n">
-        <v>25.25</v>
+        <v>437.92</v>
       </c>
       <c r="E62" t="n">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="F62" t="n">
-        <v>665</v>
+        <v>979</v>
       </c>
       <c r="G62" t="n">
-        <v>235.01</v>
+        <v>223.52</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I62" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J62" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K62" t="n">
+        <v>1598</v>
+      </c>
+      <c r="L62" t="n">
+        <v>105</v>
+      </c>
+      <c r="M62" t="n">
+        <v>1.055</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:01.587</t>
+          <t>2026-05-29 09:34:03.770</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>1779421623744</v>
+        <v>1780022042345</v>
       </c>
       <c r="C63" t="n">
-        <v>87592</v>
+        <v>77236</v>
       </c>
       <c r="D63" t="n">
-        <v>-516.02</v>
+        <v>312.02</v>
       </c>
       <c r="E63" t="n">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="F63" t="n">
-        <v>665</v>
+        <v>979</v>
       </c>
       <c r="G63" t="n">
-        <v>235.01</v>
+        <v>223.52</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I63" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J63" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K63" t="n">
+        <v>1424</v>
+      </c>
+      <c r="L63" t="n">
+        <v>109</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0.6850000000000001</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:01.897</t>
+          <t>2026-05-29 09:34:04.109</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>1779421623946</v>
+        <v>1780022042545</v>
       </c>
       <c r="C64" t="n">
-        <v>87820</v>
+        <v>77246</v>
       </c>
       <c r="D64" t="n">
-        <v>-262.22</v>
+        <v>306.42</v>
       </c>
       <c r="E64" t="n">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="F64" t="n">
-        <v>665</v>
+        <v>979</v>
       </c>
       <c r="G64" t="n">
-        <v>235.01</v>
+        <v>223.52</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I64" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J64" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K64" t="n">
+        <v>1563</v>
+      </c>
+      <c r="L64" t="n">
+        <v>107</v>
+      </c>
+      <c r="M64" t="n">
+        <v>0.847</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:01.923</t>
+          <t>2026-05-29 09:34:04.110</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>1779421624147</v>
+        <v>1780022042745</v>
       </c>
       <c r="C65" t="n">
-        <v>88123</v>
+        <v>77867</v>
       </c>
       <c r="D65" t="n">
-        <v>53.89</v>
+        <v>912.1</v>
       </c>
       <c r="E65" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F65" t="n">
-        <v>785</v>
+        <v>979</v>
       </c>
       <c r="G65" t="n">
-        <v>234.29</v>
+        <v>223.52</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I65" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J65" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K65" t="n">
+        <v>1364</v>
+      </c>
+      <c r="L65" t="n">
+        <v>112</v>
+      </c>
+      <c r="M65" t="n">
+        <v>0.763</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:02.711</t>
+          <t>2026-05-29 09:34:04.111</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>1779421624348</v>
+        <v>1780022042945</v>
       </c>
       <c r="C66" t="n">
-        <v>88193</v>
+        <v>78404</v>
       </c>
       <c r="D66" t="n">
-        <v>121.2</v>
+        <v>1403.5</v>
       </c>
       <c r="E66" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F66" t="n">
-        <v>785</v>
+        <v>979</v>
       </c>
       <c r="G66" t="n">
-        <v>234.29</v>
+        <v>223.52</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I66" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J66" t="n">
+        <v>34.49</v>
+      </c>
+      <c r="K66" t="n">
+        <v>1165</v>
+      </c>
+      <c r="L66" t="n">
+        <v>109</v>
+      </c>
+      <c r="M66" t="n">
+        <v>0.979</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:02.712</t>
+          <t>2026-05-29 09:34:04.444</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>1779421624550</v>
+        <v>1780022043145</v>
       </c>
       <c r="C67" t="n">
-        <v>87870</v>
+        <v>78094</v>
       </c>
       <c r="D67" t="n">
-        <v>-207.86</v>
+        <v>1023.32</v>
       </c>
       <c r="E67" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F67" t="n">
-        <v>785</v>
+        <v>979</v>
       </c>
       <c r="G67" t="n">
-        <v>234.29</v>
+        <v>223.52</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I67" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J67" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K67" t="n">
+        <v>1298</v>
+      </c>
+      <c r="L67" t="n">
+        <v>104</v>
+      </c>
+      <c r="M67" t="n">
+        <v>0.981</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:02.712</t>
+          <t>2026-05-29 09:34:04.695</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>1779421624751</v>
+        <v>1780022043364</v>
       </c>
       <c r="C68" t="n">
-        <v>88026</v>
+        <v>78438</v>
       </c>
       <c r="D68" t="n">
-        <v>-41.47</v>
+        <v>1316.16</v>
       </c>
       <c r="E68" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F68" t="n">
-        <v>785</v>
+        <v>979</v>
       </c>
       <c r="G68" t="n">
-        <v>234.29</v>
+        <v>223.52</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I68" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J68" t="n">
+        <v>34.49</v>
+      </c>
+      <c r="K68" t="n">
+        <v>1328</v>
+      </c>
+      <c r="L68" t="n">
+        <v>112</v>
+      </c>
+      <c r="M68" t="n">
+        <v>2.632</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:02.713</t>
+          <t>2026-05-29 09:34:04.697</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>1779421624953</v>
+        <v>1780022043564</v>
       </c>
       <c r="C69" t="n">
-        <v>88244</v>
+        <v>78385</v>
       </c>
       <c r="D69" t="n">
-        <v>178.61</v>
+        <v>1197.35</v>
       </c>
       <c r="E69" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F69" t="n">
-        <v>745</v>
+        <v>979</v>
       </c>
       <c r="G69" t="n">
-        <v>235.24</v>
+        <v>223.52</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I69" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J69" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K69" t="n">
+        <v>1132</v>
+      </c>
+      <c r="L69" t="n">
+        <v>108</v>
+      </c>
+      <c r="M69" t="n">
+        <v>1.084</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:03.320</t>
+          <t>2026-05-29 09:34:06.086</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>1779421625154</v>
+        <v>1780022043765</v>
       </c>
       <c r="C70" t="n">
-        <v>87751</v>
+        <v>77497</v>
       </c>
       <c r="D70" t="n">
-        <v>-323.32</v>
+        <v>249.48</v>
       </c>
       <c r="E70" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F70" t="n">
-        <v>745</v>
+        <v>979</v>
       </c>
       <c r="G70" t="n">
-        <v>235.24</v>
+        <v>223.52</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I70" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J70" t="n">
+        <v>34.49</v>
+      </c>
+      <c r="K70" t="n">
+        <v>2320</v>
+      </c>
+      <c r="L70" t="n">
+        <v>106</v>
+      </c>
+      <c r="M70" t="n">
+        <v>0.718</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:03.321</t>
+          <t>2026-05-29 09:34:06.088</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>1779421625355</v>
+        <v>1780022043964</v>
       </c>
       <c r="C71" t="n">
-        <v>87935</v>
+        <v>77282</v>
       </c>
       <c r="D71" t="n">
-        <v>-123.16</v>
+        <v>22.01</v>
       </c>
       <c r="E71" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F71" t="n">
-        <v>745</v>
+        <v>979</v>
       </c>
       <c r="G71" t="n">
-        <v>235.24</v>
+        <v>223.52</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I71" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J71" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K71" t="n">
+        <v>2123</v>
+      </c>
+      <c r="L71" t="n">
+        <v>110</v>
+      </c>
+      <c r="M71" t="n">
+        <v>1.358</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:03.322</t>
+          <t>2026-05-29 09:34:06.106</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>1779421625557</v>
+        <v>1780022044164</v>
       </c>
       <c r="C72" t="n">
-        <v>88155</v>
+        <v>77510</v>
       </c>
       <c r="D72" t="n">
-        <v>103</v>
+        <v>248.91</v>
       </c>
       <c r="E72" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F72" t="n">
-        <v>745</v>
+        <v>979</v>
       </c>
       <c r="G72" t="n">
-        <v>235.24</v>
+        <v>223.52</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I72" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J72" t="n">
+        <v>34.49</v>
+      </c>
+      <c r="K72" t="n">
+        <v>1941</v>
+      </c>
+      <c r="L72" t="n">
+        <v>108</v>
+      </c>
+      <c r="M72" t="n">
+        <v>0.8090000000000001</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:03.729</t>
+          <t>2026-05-29 09:34:06.132</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>1779421625758</v>
+        <v>1780022044364</v>
       </c>
       <c r="C73" t="n">
-        <v>87981</v>
+        <v>77419</v>
       </c>
       <c r="D73" t="n">
-        <v>-76.15000000000001</v>
+        <v>145.46</v>
       </c>
       <c r="E73" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="F73" t="n">
-        <v>745</v>
+        <v>979</v>
       </c>
       <c r="G73" t="n">
-        <v>227.46</v>
+        <v>223.52</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I73" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J73" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K73" t="n">
+        <v>1767</v>
+      </c>
+      <c r="L73" t="n">
+        <v>106</v>
+      </c>
+      <c r="M73" t="n">
+        <v>0.777</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:03.730</t>
+          <t>2026-05-29 09:34:06.165</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>1779421625960</v>
+        <v>1780022044564</v>
       </c>
       <c r="C74" t="n">
-        <v>87801</v>
+        <v>77632</v>
       </c>
       <c r="D74" t="n">
-        <v>-252.34</v>
+        <v>351.19</v>
       </c>
       <c r="E74" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="F74" t="n">
-        <v>745</v>
+        <v>979</v>
       </c>
       <c r="G74" t="n">
-        <v>227.46</v>
+        <v>223.52</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I74" t="n">
+        <v>49.28</v>
+      </c>
+      <c r="J74" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K74" t="n">
+        <v>1599</v>
+      </c>
+      <c r="L74" t="n">
+        <v>107</v>
+      </c>
+      <c r="M74" t="n">
+        <v>1.703</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:04.145</t>
+          <t>2026-05-29 09:34:06.166</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>1779421626161</v>
+        <v>1780022044764</v>
       </c>
       <c r="C75" t="n">
-        <v>87990</v>
+        <v>77948</v>
       </c>
       <c r="D75" t="n">
-        <v>-50.73</v>
+        <v>649.63</v>
       </c>
       <c r="E75" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="F75" t="n">
-        <v>745</v>
+        <v>5298</v>
       </c>
       <c r="G75" t="n">
-        <v>227.46</v>
+        <v>223.52</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I75" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J75" t="n">
+        <v>34.49</v>
+      </c>
+      <c r="K75" t="n">
+        <v>1401</v>
+      </c>
+      <c r="L75" t="n">
+        <v>110</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.62</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:04.146</t>
+          <t>2026-05-29 09:34:06.264</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>1779421626362</v>
+        <v>1780022044964</v>
       </c>
       <c r="C76" t="n">
-        <v>88212</v>
+        <v>77941</v>
       </c>
       <c r="D76" t="n">
-        <v>173.81</v>
+        <v>610.15</v>
       </c>
       <c r="E76" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="F76" t="n">
-        <v>685</v>
+        <v>5298</v>
       </c>
       <c r="G76" t="n">
-        <v>231.58</v>
+        <v>223.52</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I76" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J76" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K76" t="n">
+        <v>1299</v>
+      </c>
+      <c r="L76" t="n">
+        <v>115</v>
+      </c>
+      <c r="M76" t="n">
+        <v>0.551</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:04.858</t>
+          <t>2026-05-29 09:34:06.794</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>1779421626564</v>
+        <v>1780022045183</v>
       </c>
       <c r="C77" t="n">
-        <v>87778</v>
+        <v>78112</v>
       </c>
       <c r="D77" t="n">
-        <v>-268.88</v>
+        <v>750.64</v>
       </c>
       <c r="E77" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="F77" t="n">
-        <v>685</v>
+        <v>5298</v>
       </c>
       <c r="G77" t="n">
-        <v>231.58</v>
+        <v>223.52</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I77" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J77" t="n">
+        <v>34.49</v>
+      </c>
+      <c r="K77" t="n">
+        <v>1610</v>
+      </c>
+      <c r="L77" t="n">
+        <v>115</v>
+      </c>
+      <c r="M77" t="n">
+        <v>0.994</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:04.859</t>
+          <t>2026-05-29 09:34:06.795</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>1779421626765</v>
+        <v>1780022045383</v>
       </c>
       <c r="C78" t="n">
-        <v>88051</v>
+        <v>78263</v>
       </c>
       <c r="D78" t="n">
-        <v>17.56</v>
+        <v>864.11</v>
       </c>
       <c r="E78" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="F78" t="n">
-        <v>685</v>
+        <v>5298</v>
       </c>
       <c r="G78" t="n">
-        <v>231.58</v>
+        <v>223.52</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I78" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J78" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K78" t="n">
+        <v>1411</v>
+      </c>
+      <c r="L78" t="n">
+        <v>114</v>
+      </c>
+      <c r="M78" t="n">
+        <v>1.18</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:04.889</t>
+          <t>2026-05-29 09:34:06.797</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>1779421626967</v>
+        <v>1780022045583</v>
       </c>
       <c r="C79" t="n">
-        <v>88326</v>
+        <v>78553</v>
       </c>
       <c r="D79" t="n">
-        <v>291.69</v>
+        <v>1110.9</v>
       </c>
       <c r="E79" t="n">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="F79" t="n">
-        <v>584</v>
+        <v>5298</v>
       </c>
       <c r="G79" t="n">
-        <v>246.16</v>
+        <v>223.52</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I79" t="n">
+        <v>49.28</v>
+      </c>
+      <c r="J79" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K79" t="n">
+        <v>1213</v>
+      </c>
+      <c r="L79" t="n">
+        <v>113</v>
+      </c>
+      <c r="M79" t="n">
+        <v>0.983</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:05.076</t>
+          <t>2026-05-29 09:34:07.789</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>1779421627168</v>
+        <v>1780022045783</v>
       </c>
       <c r="C80" t="n">
-        <v>87733</v>
+        <v>78677</v>
       </c>
       <c r="D80" t="n">
-        <v>-315.9</v>
+        <v>1179.36</v>
       </c>
       <c r="E80" t="n">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="F80" t="n">
-        <v>584</v>
+        <v>5298</v>
       </c>
       <c r="G80" t="n">
-        <v>246.16</v>
+        <v>223.52</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I80" t="n">
+        <v>49.26</v>
+      </c>
+      <c r="J80" t="n">
+        <v>34.49</v>
+      </c>
+      <c r="K80" t="n">
+        <v>2004</v>
+      </c>
+      <c r="L80" t="n">
+        <v>111</v>
+      </c>
+      <c r="M80" t="n">
+        <v>1.269</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:05.379</t>
+          <t>2026-05-29 09:34:07.790</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>1779421627369</v>
+        <v>1780022045983</v>
       </c>
       <c r="C81" t="n">
-        <v>87922</v>
+        <v>78897</v>
       </c>
       <c r="D81" t="n">
-        <v>-111.1</v>
+        <v>1340.39</v>
       </c>
       <c r="E81" t="n">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="F81" t="n">
-        <v>584</v>
+        <v>5298</v>
       </c>
       <c r="G81" t="n">
-        <v>246.16</v>
+        <v>223.52</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I81" t="n">
+        <v>49.28</v>
+      </c>
+      <c r="J81" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K81" t="n">
+        <v>1806</v>
+      </c>
+      <c r="L81" t="n">
+        <v>117</v>
+      </c>
+      <c r="M81" t="n">
+        <v>0.959</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:05.380</t>
+          <t>2026-05-29 09:34:07.802</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>1779421627571</v>
+        <v>1780022046183</v>
       </c>
       <c r="C82" t="n">
-        <v>87990</v>
+        <v>79804</v>
       </c>
       <c r="D82" t="n">
-        <v>-37.55</v>
+        <v>2180.37</v>
       </c>
       <c r="E82" t="n">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="F82" t="n">
-        <v>584</v>
+        <v>5298</v>
       </c>
       <c r="G82" t="n">
-        <v>246.16</v>
+        <v>223.52</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I82" t="n">
+        <v>49.28</v>
+      </c>
+      <c r="J82" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K82" t="n">
+        <v>1617</v>
+      </c>
+      <c r="L82" t="n">
+        <v>104</v>
+      </c>
+      <c r="M82" t="n">
+        <v>1.842</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:05.790</t>
+          <t>2026-05-29 09:34:07.943</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>1779421627772</v>
+        <v>1780022046383</v>
       </c>
       <c r="C83" t="n">
-        <v>88304</v>
+        <v>79316</v>
       </c>
       <c r="D83" t="n">
-        <v>278.33</v>
+        <v>1583.35</v>
       </c>
       <c r="E83" t="n">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="F83" t="n">
-        <v>826</v>
+        <v>5298</v>
       </c>
       <c r="G83" t="n">
-        <v>245.3</v>
+        <v>223.52</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I83" t="n">
+        <v>49.42</v>
+      </c>
+      <c r="J83" t="n">
+        <v>34.49</v>
+      </c>
+      <c r="K83" t="n">
+        <v>1558</v>
+      </c>
+      <c r="L83" t="n">
+        <v>125</v>
+      </c>
+      <c r="M83" t="n">
+        <v>1.878</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:05.791</t>
+          <t>2026-05-29 09:34:07.945</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>1779421627974</v>
+        <v>1780022046583</v>
       </c>
       <c r="C84" t="n">
-        <v>87773</v>
+        <v>79486</v>
       </c>
       <c r="D84" t="n">
-        <v>-266.59</v>
+        <v>1674.18</v>
       </c>
       <c r="E84" t="n">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="F84" t="n">
-        <v>826</v>
+        <v>5298</v>
       </c>
       <c r="G84" t="n">
-        <v>245.3</v>
+        <v>223.52</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I84" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J84" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K84" t="n">
+        <v>1361</v>
+      </c>
+      <c r="L84" t="n">
+        <v>118</v>
+      </c>
+      <c r="M84" t="n">
+        <v>0.876</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:06.197</t>
+          <t>2026-05-29 09:34:07.946</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>1779421628175</v>
+        <v>1780022046783</v>
       </c>
       <c r="C85" t="n">
-        <v>87997</v>
+        <v>80020</v>
       </c>
       <c r="D85" t="n">
-        <v>-29.26</v>
+        <v>2124.47</v>
       </c>
       <c r="E85" t="n">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="F85" t="n">
-        <v>826</v>
+        <v>5298</v>
       </c>
       <c r="G85" t="n">
-        <v>245.3</v>
+        <v>223.52</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I85" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J85" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K85" t="n">
+        <v>1162</v>
+      </c>
+      <c r="L85" t="n">
+        <v>109</v>
+      </c>
+      <c r="M85" t="n">
+        <v>1.049</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:06.222</t>
+          <t>2026-05-29 09:34:07.947</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>1779421628376</v>
+        <v>1780022046983</v>
       </c>
       <c r="C86" t="n">
-        <v>88252</v>
+        <v>80000</v>
       </c>
       <c r="D86" t="n">
-        <v>227.21</v>
+        <v>1998.25</v>
       </c>
       <c r="E86" t="n">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="F86" t="n">
-        <v>644</v>
+        <v>5298</v>
       </c>
       <c r="G86" t="n">
-        <v>118.54</v>
+        <v>223.52</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I86" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J86" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K86" t="n">
+        <v>963</v>
+      </c>
+      <c r="L86" t="n">
+        <v>109</v>
+      </c>
+      <c r="M86" t="n">
+        <v>1.13</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:06.601</t>
+          <t>2026-05-29 09:34:08.447</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>1779421628578</v>
+        <v>1780022047183</v>
       </c>
       <c r="C87" t="n">
-        <v>88284</v>
+        <v>80091</v>
       </c>
       <c r="D87" t="n">
-        <v>247.84</v>
+        <v>1989.34</v>
       </c>
       <c r="E87" t="n">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="F87" t="n">
-        <v>644</v>
+        <v>5298</v>
       </c>
       <c r="G87" t="n">
-        <v>118.54</v>
+        <v>223.52</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I87" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J87" t="n">
+        <v>34.98</v>
+      </c>
+      <c r="K87" t="n">
+        <v>1263</v>
+      </c>
+      <c r="L87" t="n">
+        <v>101</v>
+      </c>
+      <c r="M87" t="n">
+        <v>1.352</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:06.610</t>
+          <t>2026-05-29 09:34:08.449</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>1779421628779</v>
+        <v>1780022047402</v>
       </c>
       <c r="C88" t="n">
-        <v>87981</v>
+        <v>80222</v>
       </c>
       <c r="D88" t="n">
-        <v>-67.55</v>
+        <v>2020.87</v>
       </c>
       <c r="E88" t="n">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="F88" t="n">
-        <v>644</v>
+        <v>5298</v>
       </c>
       <c r="G88" t="n">
-        <v>118.54</v>
+        <v>223.52</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I88" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J88" t="n">
+        <v>35.46</v>
+      </c>
+      <c r="K88" t="n">
+        <v>1046</v>
+      </c>
+      <c r="L88" t="n">
+        <v>116</v>
+      </c>
+      <c r="M88" t="n">
+        <v>1.429</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:07.234</t>
+          <t>2026-05-29 09:34:09.614</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>1779421628980</v>
+        <v>1780022047603</v>
       </c>
       <c r="C89" t="n">
-        <v>88175</v>
+        <v>79920</v>
       </c>
       <c r="D89" t="n">
-        <v>129.83</v>
+        <v>1617.83</v>
       </c>
       <c r="E89" t="n">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="F89" t="n">
-        <v>644</v>
+        <v>5298</v>
       </c>
       <c r="G89" t="n">
-        <v>118.54</v>
+        <v>223.52</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I89" t="n">
+        <v>49.98</v>
+      </c>
+      <c r="J89" t="n">
+        <v>34.76</v>
+      </c>
+      <c r="K89" t="n">
+        <v>2011</v>
+      </c>
+      <c r="L89" t="n">
+        <v>129</v>
+      </c>
+      <c r="M89" t="n">
+        <v>0.906</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:07.276</t>
+          <t>2026-05-29 09:34:09.616</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>1779421629182</v>
+        <v>1780022047802</v>
       </c>
       <c r="C90" t="n">
-        <v>88474</v>
+        <v>80216</v>
       </c>
       <c r="D90" t="n">
-        <v>422.34</v>
+        <v>1832.94</v>
       </c>
       <c r="E90" t="n">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="F90" t="n">
-        <v>745</v>
+        <v>5298</v>
       </c>
       <c r="G90" t="n">
-        <v>116.85</v>
+        <v>223.52</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I90" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J90" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K90" t="n">
+        <v>1813</v>
+      </c>
+      <c r="L90" t="n">
+        <v>125</v>
+      </c>
+      <c r="M90" t="n">
+        <v>0.949</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:07.277</t>
+          <t>2026-05-29 09:34:09.617</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>1779421629383</v>
+        <v>1780022048002</v>
       </c>
       <c r="C91" t="n">
-        <v>88096</v>
+        <v>80471</v>
       </c>
       <c r="D91" t="n">
-        <v>23.22</v>
+        <v>1996.29</v>
       </c>
       <c r="E91" t="n">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="F91" t="n">
-        <v>745</v>
+        <v>3198</v>
       </c>
       <c r="G91" t="n">
-        <v>116.85</v>
+        <v>223.52</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I91" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J91" t="n">
+        <v>34.98</v>
+      </c>
+      <c r="K91" t="n">
+        <v>1614</v>
+      </c>
+      <c r="L91" t="n">
+        <v>104</v>
+      </c>
+      <c r="M91" t="n">
+        <v>1.088</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:07.658</t>
+          <t>2026-05-29 09:34:10.130</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>1779421629585</v>
+        <v>1780022048202</v>
       </c>
       <c r="C92" t="n">
-        <v>88301</v>
+        <v>80710</v>
       </c>
       <c r="D92" t="n">
-        <v>227.06</v>
+        <v>2135.48</v>
       </c>
       <c r="E92" t="n">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="F92" t="n">
-        <v>745</v>
+        <v>3198</v>
       </c>
       <c r="G92" t="n">
-        <v>116.85</v>
+        <v>223.52</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I92" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J92" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K92" t="n">
+        <v>1927</v>
+      </c>
+      <c r="L92" t="n">
+        <v>110</v>
+      </c>
+      <c r="M92" t="n">
+        <v>0.5629999999999999</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:07.658</t>
+          <t>2026-05-29 09:34:10.132</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>1779421629786</v>
+        <v>1780022048402</v>
       </c>
       <c r="C93" t="n">
-        <v>88457</v>
+        <v>81614</v>
       </c>
       <c r="D93" t="n">
-        <v>371.71</v>
+        <v>2932.7</v>
       </c>
       <c r="E93" t="n">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="F93" t="n">
-        <v>745</v>
+        <v>3198</v>
       </c>
       <c r="G93" t="n">
-        <v>116.85</v>
+        <v>223.52</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I93" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J93" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K93" t="n">
+        <v>1729</v>
+      </c>
+      <c r="L93" t="n">
+        <v>109</v>
+      </c>
+      <c r="M93" t="n">
+        <v>1.227</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:08.039</t>
+          <t>2026-05-29 09:34:10.134</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>1779421629987</v>
+        <v>1780022048602</v>
       </c>
       <c r="C94" t="n">
-        <v>88704</v>
+        <v>82072</v>
       </c>
       <c r="D94" t="n">
-        <v>600.12</v>
+        <v>3244.07</v>
       </c>
       <c r="E94" t="n">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="F94" t="n">
-        <v>705</v>
+        <v>3198</v>
       </c>
       <c r="G94" t="n">
-        <v>71.16</v>
+        <v>223.52</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I94" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J94" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K94" t="n">
+        <v>1531</v>
+      </c>
+      <c r="L94" t="n">
+        <v>109</v>
+      </c>
+      <c r="M94" t="n">
+        <v>1.046</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:08.040</t>
+          <t>2026-05-29 09:34:10.147</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>1779421630189</v>
+        <v>1780022048802</v>
       </c>
       <c r="C95" t="n">
-        <v>88099</v>
+        <v>82369</v>
       </c>
       <c r="D95" t="n">
-        <v>-34.88</v>
+        <v>3378.86</v>
       </c>
       <c r="E95" t="n">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="F95" t="n">
-        <v>705</v>
+        <v>3198</v>
       </c>
       <c r="G95" t="n">
-        <v>71.16</v>
+        <v>223.52</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I95" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J95" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K95" t="n">
+        <v>1344</v>
+      </c>
+      <c r="L95" t="n">
+        <v>111</v>
+      </c>
+      <c r="M95" t="n">
+        <v>1.595</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:08.436</t>
+          <t>2026-05-29 09:34:10.985</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>1779421630390</v>
+        <v>1780022049002</v>
       </c>
       <c r="C96" t="n">
-        <v>88282</v>
+        <v>83009</v>
       </c>
       <c r="D96" t="n">
-        <v>149.86</v>
+        <v>3849.92</v>
       </c>
       <c r="E96" t="n">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="F96" t="n">
-        <v>705</v>
+        <v>3198</v>
       </c>
       <c r="G96" t="n">
-        <v>71.16</v>
+        <v>223.52</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I96" t="n">
+        <v>49.28</v>
+      </c>
+      <c r="J96" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K96" t="n">
+        <v>1981</v>
+      </c>
+      <c r="L96" t="n">
+        <v>107</v>
+      </c>
+      <c r="M96" t="n">
+        <v>1.799</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:08.441</t>
+          <t>2026-05-29 09:34:10.994</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>1779421630592</v>
+        <v>1780022049202</v>
       </c>
       <c r="C97" t="n">
-        <v>88565</v>
+        <v>83837</v>
       </c>
       <c r="D97" t="n">
-        <v>425.37</v>
+        <v>4485.42</v>
       </c>
       <c r="E97" t="n">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="F97" t="n">
-        <v>705</v>
+        <v>3198</v>
       </c>
       <c r="G97" t="n">
-        <v>71.16</v>
+        <v>223.52</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I97" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J97" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K97" t="n">
+        <v>1790</v>
+      </c>
+      <c r="L97" t="n">
+        <v>117</v>
+      </c>
+      <c r="M97" t="n">
+        <v>1.318</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:08.875</t>
+          <t>2026-05-29 09:34:10.996</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>1779421630793</v>
+        <v>1780022049421</v>
       </c>
       <c r="C98" t="n">
-        <v>88737</v>
+        <v>82169</v>
       </c>
       <c r="D98" t="n">
-        <v>576.1</v>
+        <v>2593.15</v>
       </c>
       <c r="E98" t="n">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="F98" t="n">
-        <v>846</v>
+        <v>3198</v>
       </c>
       <c r="G98" t="n">
-        <v>80.09</v>
+        <v>223.52</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I98" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J98" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K98" t="n">
+        <v>1573</v>
+      </c>
+      <c r="L98" t="n">
+        <v>106</v>
+      </c>
+      <c r="M98" t="n">
+        <v>1.495</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:08.875</t>
+          <t>2026-05-29 09:34:10.999</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>1779421630994</v>
+        <v>1780022049621</v>
       </c>
       <c r="C99" t="n">
-        <v>88137</v>
+        <v>81828</v>
       </c>
       <c r="D99" t="n">
-        <v>-52.71</v>
+        <v>2122.5</v>
       </c>
       <c r="E99" t="n">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="F99" t="n">
-        <v>846</v>
+        <v>3198</v>
       </c>
       <c r="G99" t="n">
-        <v>80.09</v>
+        <v>223.52</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I99" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J99" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K99" t="n">
+        <v>1376</v>
+      </c>
+      <c r="L99" t="n">
+        <v>113</v>
+      </c>
+      <c r="M99" t="n">
+        <v>1.954</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:09.287</t>
+          <t>2026-05-29 09:34:11.575</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>1779421631196</v>
+        <v>1780022049821</v>
       </c>
       <c r="C100" t="n">
-        <v>88409</v>
+        <v>81690</v>
       </c>
       <c r="D100" t="n">
-        <v>221.93</v>
+        <v>1878.37</v>
       </c>
       <c r="E100" t="n">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="F100" t="n">
-        <v>846</v>
+        <v>3198</v>
       </c>
       <c r="G100" t="n">
-        <v>80.09</v>
+        <v>223.52</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I100" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J100" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K100" t="n">
+        <v>1751</v>
+      </c>
+      <c r="L100" t="n">
+        <v>115</v>
+      </c>
+      <c r="M100" t="n">
+        <v>2.252</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:09.288</t>
+          <t>2026-05-29 09:34:11.602</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>1779421631397</v>
+        <v>1780022050021</v>
       </c>
       <c r="C101" t="n">
-        <v>88739</v>
+        <v>81289</v>
       </c>
       <c r="D101" t="n">
-        <v>540.83</v>
+        <v>1383.45</v>
       </c>
       <c r="E101" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F101" t="n">
-        <v>745</v>
+        <v>3198</v>
       </c>
       <c r="G101" t="n">
-        <v>78.06</v>
+        <v>223.52</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I101" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J101" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K101" t="n">
+        <v>1579</v>
+      </c>
+      <c r="L101" t="n">
+        <v>108</v>
+      </c>
+      <c r="M101" t="n">
+        <v>1.397</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:09.692</t>
+          <t>2026-05-29 09:34:11.604</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>1779421631598</v>
+        <v>1780022050221</v>
       </c>
       <c r="C102" t="n">
-        <v>88666</v>
+        <v>81246</v>
       </c>
       <c r="D102" t="n">
-        <v>440.79</v>
+        <v>1271.28</v>
       </c>
       <c r="E102" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F102" t="n">
-        <v>745</v>
+        <v>3198</v>
       </c>
       <c r="G102" t="n">
-        <v>78.06</v>
+        <v>223.52</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I102" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J102" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K102" t="n">
+        <v>1382</v>
+      </c>
+      <c r="L102" t="n">
+        <v>110</v>
+      </c>
+      <c r="M102" t="n">
+        <v>1.073</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:09.697</t>
+          <t>2026-05-29 09:34:11.652</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>1779421631800</v>
+        <v>1780022050421</v>
       </c>
       <c r="C103" t="n">
-        <v>88245</v>
+        <v>81863</v>
       </c>
       <c r="D103" t="n">
-        <v>-2.25</v>
+        <v>1824.72</v>
       </c>
       <c r="E103" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F103" t="n">
-        <v>745</v>
+        <v>3198</v>
       </c>
       <c r="G103" t="n">
-        <v>78.06</v>
+        <v>223.52</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I103" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J103" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K103" t="n">
+        <v>1229</v>
+      </c>
+      <c r="L103" t="n">
+        <v>107</v>
+      </c>
+      <c r="M103" t="n">
+        <v>1.086</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:10.076</t>
+          <t>2026-05-29 09:34:11.932</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>1779421632001</v>
+        <v>1780022050621</v>
       </c>
       <c r="C104" t="n">
-        <v>88405</v>
+        <v>82550</v>
       </c>
       <c r="D104" t="n">
-        <v>157.86</v>
+        <v>2420.48</v>
       </c>
       <c r="E104" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F104" t="n">
-        <v>745</v>
+        <v>3198</v>
       </c>
       <c r="G104" t="n">
-        <v>78.06</v>
+        <v>223.52</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I104" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J104" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K104" t="n">
+        <v>1311</v>
+      </c>
+      <c r="L104" t="n">
+        <v>112</v>
+      </c>
+      <c r="M104" t="n">
+        <v>0.777</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:10.077</t>
+          <t>2026-05-29 09:34:13.379</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>1779421632203</v>
+        <v>1780022050821</v>
       </c>
       <c r="C105" t="n">
-        <v>88652</v>
+        <v>82670</v>
       </c>
       <c r="D105" t="n">
-        <v>396.97</v>
+        <v>2419.46</v>
       </c>
       <c r="E105" t="n">
         <v>77</v>
       </c>
       <c r="F105" t="n">
-        <v>806</v>
+        <v>3198</v>
       </c>
       <c r="G105" t="n">
-        <v>81.91</v>
+        <v>223.52</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I105" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J105" t="n">
+        <v>35.47</v>
+      </c>
+      <c r="K105" t="n">
+        <v>2556</v>
+      </c>
+      <c r="L105" t="n">
+        <v>111</v>
+      </c>
+      <c r="M105" t="n">
+        <v>1.873</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:10.492</t>
+          <t>2026-05-29 09:34:13.381</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>1779421632404</v>
+        <v>1780022051201</v>
       </c>
       <c r="C106" t="n">
-        <v>88101</v>
+        <v>83471</v>
       </c>
       <c r="D106" t="n">
-        <v>-173.88</v>
+        <v>3099.48</v>
       </c>
       <c r="E106" t="n">
         <v>77</v>
       </c>
       <c r="F106" t="n">
-        <v>806</v>
+        <v>3198</v>
       </c>
       <c r="G106" t="n">
-        <v>81.91</v>
+        <v>223.52</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I106" t="n">
+        <v>40.25</v>
+      </c>
+      <c r="J106" t="n">
+        <v>34.98</v>
+      </c>
+      <c r="K106" t="n">
+        <v>2178</v>
+      </c>
+      <c r="L106" t="n">
+        <v>124</v>
+      </c>
+      <c r="M106" t="n">
+        <v>1.681</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:10.493</t>
+          <t>2026-05-29 09:34:13.382</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>1779421632605</v>
+        <v>1780022051420</v>
       </c>
       <c r="C107" t="n">
-        <v>88278</v>
+        <v>82895</v>
       </c>
       <c r="D107" t="n">
-        <v>11.82</v>
+        <v>2368.51</v>
       </c>
       <c r="E107" t="n">
         <v>77</v>
       </c>
       <c r="F107" t="n">
-        <v>806</v>
+        <v>3198</v>
       </c>
       <c r="G107" t="n">
-        <v>81.91</v>
+        <v>223.52</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I107" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J107" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K107" t="n">
+        <v>1961</v>
+      </c>
+      <c r="L107" t="n">
+        <v>109</v>
+      </c>
+      <c r="M107" t="n">
+        <v>0.874</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:11.024</t>
+          <t>2026-05-29 09:34:13.384</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>1779421632807</v>
+        <v>1780022051620</v>
       </c>
       <c r="C108" t="n">
-        <v>88491</v>
+        <v>82610</v>
       </c>
       <c r="D108" t="n">
-        <v>224.23</v>
+        <v>1965.08</v>
       </c>
       <c r="E108" t="n">
         <v>77</v>
       </c>
       <c r="F108" t="n">
-        <v>806</v>
+        <v>3198</v>
       </c>
       <c r="G108" t="n">
-        <v>81.91</v>
+        <v>223.52</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I108" t="n">
+        <v>49.25</v>
+      </c>
+      <c r="J108" t="n">
+        <v>34.49</v>
+      </c>
+      <c r="K108" t="n">
+        <v>1763</v>
+      </c>
+      <c r="L108" t="n">
+        <v>109</v>
+      </c>
+      <c r="M108" t="n">
+        <v>0.97</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:11.025</t>
+          <t>2026-05-29 09:34:13.385</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>1779421633008</v>
+        <v>1780022051820</v>
       </c>
       <c r="C109" t="n">
-        <v>88450</v>
+        <v>83201</v>
       </c>
       <c r="D109" t="n">
-        <v>172.01</v>
+        <v>2457.83</v>
       </c>
       <c r="E109" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F109" t="n">
-        <v>644</v>
+        <v>3198</v>
       </c>
       <c r="G109" t="n">
-        <v>86.39</v>
+        <v>223.52</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I109" t="n">
+        <v>49.28</v>
+      </c>
+      <c r="J109" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K109" t="n">
+        <v>1564</v>
+      </c>
+      <c r="L109" t="n">
+        <v>116</v>
+      </c>
+      <c r="M109" t="n">
+        <v>1.216</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:11.025</t>
+          <t>2026-05-29 09:34:13.387</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>1779421633210</v>
+        <v>1780022052020</v>
       </c>
       <c r="C110" t="n">
-        <v>87977</v>
+        <v>84221</v>
       </c>
       <c r="D110" t="n">
-        <v>-309.59</v>
+        <v>3354.94</v>
       </c>
       <c r="E110" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F110" t="n">
-        <v>644</v>
+        <v>3998</v>
       </c>
       <c r="G110" t="n">
-        <v>86.39</v>
+        <v>223.52</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I110" t="n">
+        <v>49.28</v>
+      </c>
+      <c r="J110" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K110" t="n">
+        <v>1365</v>
+      </c>
+      <c r="L110" t="n">
+        <v>108</v>
+      </c>
+      <c r="M110" t="n">
+        <v>1.374</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:11.318</t>
+          <t>2026-05-29 09:34:13.388</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>1779421633411</v>
+        <v>1780022052220</v>
       </c>
       <c r="C111" t="n">
-        <v>88187</v>
+        <v>83574</v>
       </c>
       <c r="D111" t="n">
-        <v>-84.11</v>
+        <v>2540.19</v>
       </c>
       <c r="E111" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F111" t="n">
-        <v>644</v>
+        <v>3998</v>
       </c>
       <c r="G111" t="n">
-        <v>86.39</v>
+        <v>223.52</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I111" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J111" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K111" t="n">
+        <v>1167</v>
+      </c>
+      <c r="L111" t="n">
+        <v>112</v>
+      </c>
+      <c r="M111" t="n">
+        <v>1.151</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:11.768</t>
+          <t>2026-05-29 09:34:13.694</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>1779421633612</v>
+        <v>1780022052420</v>
       </c>
       <c r="C112" t="n">
-        <v>88429</v>
+        <v>83354</v>
       </c>
       <c r="D112" t="n">
-        <v>162.1</v>
+        <v>2193.18</v>
       </c>
       <c r="E112" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F112" t="n">
-        <v>644</v>
+        <v>3998</v>
       </c>
       <c r="G112" t="n">
-        <v>86.39</v>
+        <v>223.52</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I112" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J112" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K112" t="n">
+        <v>1272</v>
+      </c>
+      <c r="L112" t="n">
+        <v>109</v>
+      </c>
+      <c r="M112" t="n">
+        <v>2.092</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:11.769</t>
+          <t>2026-05-29 09:34:13.697</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>1779421633814</v>
+        <v>1780022052620</v>
       </c>
       <c r="C113" t="n">
-        <v>88143</v>
+        <v>83041</v>
       </c>
       <c r="D113" t="n">
-        <v>-132.01</v>
+        <v>1770.52</v>
       </c>
       <c r="E113" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="F113" t="n">
-        <v>786</v>
+        <v>3998</v>
       </c>
       <c r="G113" t="n">
-        <v>87.34999999999999</v>
+        <v>223.52</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I113" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J113" t="n">
+        <v>35.46</v>
+      </c>
+      <c r="K113" t="n">
+        <v>1075</v>
+      </c>
+      <c r="L113" t="n">
+        <v>114</v>
+      </c>
+      <c r="M113" t="n">
+        <v>2.309</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:12.129</t>
+          <t>2026-05-29 09:34:13.950</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>1779421634015</v>
+        <v>1780022052821</v>
       </c>
       <c r="C114" t="n">
-        <v>87980</v>
+        <v>82369</v>
       </c>
       <c r="D114" t="n">
-        <v>-288.41</v>
+        <v>1010</v>
       </c>
       <c r="E114" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="F114" t="n">
-        <v>786</v>
+        <v>3998</v>
       </c>
       <c r="G114" t="n">
-        <v>87.34999999999999</v>
+        <v>223.52</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I114" t="n">
+        <v>49.51</v>
+      </c>
+      <c r="J114" t="n">
+        <v>35.47</v>
+      </c>
+      <c r="K114" t="n">
+        <v>1127</v>
+      </c>
+      <c r="L114" t="n">
+        <v>129</v>
+      </c>
+      <c r="M114" t="n">
+        <v>1.016</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:12.130</t>
+          <t>2026-05-29 09:34:13.995</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>1779421634217</v>
+        <v>1780022053020</v>
       </c>
       <c r="C115" t="n">
-        <v>88058</v>
+        <v>81355</v>
       </c>
       <c r="D115" t="n">
-        <v>-195.99</v>
+        <v>-54.5</v>
       </c>
       <c r="E115" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="F115" t="n">
-        <v>786</v>
+        <v>3998</v>
       </c>
       <c r="G115" t="n">
-        <v>87.34999999999999</v>
+        <v>223.52</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I115" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J115" t="n">
+        <v>34.98</v>
+      </c>
+      <c r="K115" t="n">
+        <v>974</v>
+      </c>
+      <c r="L115" t="n">
+        <v>116</v>
+      </c>
+      <c r="M115" t="n">
+        <v>0.677</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:12.533</t>
+          <t>2026-05-29 09:34:14.021</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>1779421634418</v>
+        <v>1780022053220</v>
       </c>
       <c r="C116" t="n">
-        <v>88460</v>
+        <v>80069</v>
       </c>
       <c r="D116" t="n">
-        <v>215.81</v>
+        <v>-1337.78</v>
       </c>
       <c r="E116" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="F116" t="n">
-        <v>786</v>
+        <v>3998</v>
       </c>
       <c r="G116" t="n">
-        <v>87.34999999999999</v>
+        <v>223.52</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I116" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J116" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K116" t="n">
+        <v>800</v>
+      </c>
+      <c r="L116" t="n">
+        <v>99</v>
+      </c>
+      <c r="M116" t="n">
+        <v>1.187</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:12.533</t>
+          <t>2026-05-29 09:34:14.340</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>1779421634619</v>
+        <v>1780022053420</v>
       </c>
       <c r="C117" t="n">
-        <v>88690</v>
+        <v>80122</v>
       </c>
       <c r="D117" t="n">
-        <v>435.02</v>
+        <v>-1217.89</v>
       </c>
       <c r="E117" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F117" t="n">
-        <v>805</v>
+        <v>3998</v>
       </c>
       <c r="G117" t="n">
-        <v>72.05</v>
+        <v>223.52</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I117" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J117" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K117" t="n">
+        <v>918</v>
+      </c>
+      <c r="L117" t="n">
+        <v>113</v>
+      </c>
+      <c r="M117" t="n">
+        <v>1.739</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:13.203</t>
+          <t>2026-05-29 09:34:14.616</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>1779421634821</v>
+        <v>1780022053639</v>
       </c>
       <c r="C118" t="n">
-        <v>88497</v>
+        <v>80759</v>
       </c>
       <c r="D118" t="n">
-        <v>220.27</v>
+        <v>-520</v>
       </c>
       <c r="E118" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F118" t="n">
-        <v>805</v>
+        <v>3998</v>
       </c>
       <c r="G118" t="n">
-        <v>72.05</v>
+        <v>223.52</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I118" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J118" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K118" t="n">
+        <v>976</v>
+      </c>
+      <c r="L118" t="n">
+        <v>116</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.956</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:13.203</t>
+          <t>2026-05-29 09:34:15.621</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>1779421635022</v>
+        <v>1780022053839</v>
       </c>
       <c r="C119" t="n">
-        <v>88798</v>
+        <v>80595</v>
       </c>
       <c r="D119" t="n">
-        <v>510.26</v>
+        <v>-658</v>
       </c>
       <c r="E119" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F119" t="n">
-        <v>805</v>
+        <v>3998</v>
       </c>
       <c r="G119" t="n">
-        <v>72.05</v>
+        <v>223.52</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I119" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J119" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K119" t="n">
+        <v>1780</v>
+      </c>
+      <c r="L119" t="n">
+        <v>112</v>
+      </c>
+      <c r="M119" t="n">
+        <v>1.436</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:13.204</t>
+          <t>2026-05-29 09:34:15.623</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>1779421635223</v>
+        <v>1780022054039</v>
       </c>
       <c r="C120" t="n">
-        <v>89295</v>
+        <v>81160</v>
       </c>
       <c r="D120" t="n">
-        <v>981.74</v>
+        <v>-60.1</v>
       </c>
       <c r="E120" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F120" t="n">
-        <v>805</v>
+        <v>3998</v>
       </c>
       <c r="G120" t="n">
-        <v>72.05</v>
+        <v>223.52</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I120" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J120" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K120" t="n">
+        <v>1583</v>
+      </c>
+      <c r="L120" t="n">
+        <v>115</v>
+      </c>
+      <c r="M120" t="n">
+        <v>1.312</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:13.204</t>
+          <t>2026-05-29 09:34:15.625</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>1779421635425</v>
+        <v>1780022054239</v>
       </c>
       <c r="C121" t="n">
-        <v>88794</v>
+        <v>81689</v>
       </c>
       <c r="D121" t="n">
-        <v>431.66</v>
+        <v>471.91</v>
       </c>
       <c r="E121" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F121" t="n">
-        <v>805</v>
+        <v>3998</v>
       </c>
       <c r="G121" t="n">
-        <v>72.05</v>
+        <v>223.52</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I121" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J121" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K121" t="n">
+        <v>1384</v>
+      </c>
+      <c r="L121" t="n">
+        <v>106</v>
+      </c>
+      <c r="M121" t="n">
+        <v>1.705</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:13.552</t>
+          <t>2026-05-29 09:34:15.629</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>1779421635626</v>
+        <v>1780022054439</v>
       </c>
       <c r="C122" t="n">
-        <v>89084</v>
+        <v>82221</v>
       </c>
       <c r="D122" t="n">
-        <v>700.0700000000001</v>
+        <v>980.3099999999999</v>
       </c>
       <c r="E122" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F122" t="n">
-        <v>805</v>
+        <v>3998</v>
       </c>
       <c r="G122" t="n">
-        <v>72.05</v>
+        <v>223.52</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I122" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J122" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K122" t="n">
+        <v>1187</v>
+      </c>
+      <c r="L122" t="n">
+        <v>110</v>
+      </c>
+      <c r="M122" t="n">
+        <v>2.51</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:13.553</t>
+          <t>2026-05-29 09:34:15.829</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>1779421635828</v>
+        <v>1780022054639</v>
       </c>
       <c r="C123" t="n">
-        <v>89078</v>
+        <v>82726</v>
       </c>
       <c r="D123" t="n">
-        <v>659.0700000000001</v>
+        <v>1436.3</v>
       </c>
       <c r="E123" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="F123" t="n">
-        <v>1369</v>
+        <v>3998</v>
       </c>
       <c r="G123" t="n">
-        <v>207.89</v>
+        <v>223.52</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I123" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J123" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K123" t="n">
+        <v>1189</v>
+      </c>
+      <c r="L123" t="n">
+        <v>114</v>
+      </c>
+      <c r="M123" t="n">
+        <v>1.248</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:13.966</t>
+          <t>2026-05-29 09:34:15.832</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>1779421636029</v>
+        <v>1780022054839</v>
       </c>
       <c r="C124" t="n">
-        <v>89180</v>
+        <v>83430</v>
       </c>
       <c r="D124" t="n">
-        <v>728.12</v>
+        <v>2068.48</v>
       </c>
       <c r="E124" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="F124" t="n">
-        <v>1369</v>
+        <v>3998</v>
       </c>
       <c r="G124" t="n">
-        <v>207.89</v>
+        <v>223.52</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I124" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J124" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K124" t="n">
+        <v>991</v>
+      </c>
+      <c r="L124" t="n">
+        <v>112</v>
+      </c>
+      <c r="M124" t="n">
+        <v>1.362</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:13.967</t>
+          <t>2026-05-29 09:34:15.834</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>1779421636230</v>
+        <v>1780022055039</v>
       </c>
       <c r="C125" t="n">
-        <v>89160</v>
+        <v>83241</v>
       </c>
       <c r="D125" t="n">
-        <v>671.71</v>
+        <v>1776.06</v>
       </c>
       <c r="E125" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="F125" t="n">
-        <v>1369</v>
+        <v>3998</v>
       </c>
       <c r="G125" t="n">
-        <v>207.89</v>
+        <v>223.52</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I125" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J125" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K125" t="n">
+        <v>793</v>
+      </c>
+      <c r="L125" t="n">
+        <v>111</v>
+      </c>
+      <c r="M125" t="n">
+        <v>1.402</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:14.572</t>
+          <t>2026-05-29 09:34:16.225</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>1779421636432</v>
+        <v>1780022055239</v>
       </c>
       <c r="C126" t="n">
-        <v>89115</v>
+        <v>83747</v>
       </c>
       <c r="D126" t="n">
-        <v>593.13</v>
+        <v>2193.26</v>
       </c>
       <c r="E126" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="F126" t="n">
-        <v>625</v>
+        <v>3998</v>
       </c>
       <c r="G126" t="n">
-        <v>209.65</v>
+        <v>223.52</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I126" t="n">
+        <v>49.28</v>
+      </c>
+      <c r="J126" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K126" t="n">
+        <v>985</v>
+      </c>
+      <c r="L126" t="n">
+        <v>122</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.713</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:14.573</t>
+          <t>2026-05-29 09:34:16.227</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>1779421636633</v>
+        <v>1780022055439</v>
       </c>
       <c r="C127" t="n">
-        <v>89090</v>
+        <v>83972</v>
       </c>
       <c r="D127" t="n">
-        <v>538.47</v>
+        <v>2308.59</v>
       </c>
       <c r="E127" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="F127" t="n">
-        <v>625</v>
+        <v>3998</v>
       </c>
       <c r="G127" t="n">
-        <v>209.65</v>
+        <v>223.52</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I127" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J127" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K127" t="n">
+        <v>786</v>
+      </c>
+      <c r="L127" t="n">
+        <v>112</v>
+      </c>
+      <c r="M127" t="n">
+        <v>1.668</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:14.895</t>
+          <t>2026-05-29 09:34:17.012</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>1779421636835</v>
+        <v>1780022055639</v>
       </c>
       <c r="C128" t="n">
-        <v>88559</v>
+        <v>83405</v>
       </c>
       <c r="D128" t="n">
-        <v>-19.45</v>
+        <v>1626.16</v>
       </c>
       <c r="E128" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="F128" t="n">
-        <v>625</v>
+        <v>3998</v>
       </c>
       <c r="G128" t="n">
-        <v>209.65</v>
+        <v>223.52</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I128" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J128" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K128" t="n">
+        <v>1371</v>
+      </c>
+      <c r="L128" t="n">
+        <v>110</v>
+      </c>
+      <c r="M128" t="n">
+        <v>1.624</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:14.896</t>
+          <t>2026-05-29 09:34:17.049</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>1779421637036</v>
+        <v>1780022055858</v>
       </c>
       <c r="C129" t="n">
-        <v>88782</v>
+        <v>83869</v>
       </c>
       <c r="D129" t="n">
-        <v>204.52</v>
+        <v>2008.86</v>
       </c>
       <c r="E129" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="F129" t="n">
-        <v>625</v>
+        <v>3998</v>
       </c>
       <c r="G129" t="n">
-        <v>209.65</v>
+        <v>223.52</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I129" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J129" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K129" t="n">
+        <v>1190</v>
+      </c>
+      <c r="L129" t="n">
+        <v>109</v>
+      </c>
+      <c r="M129" t="n">
+        <v>1.505</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:15.687</t>
+          <t>2026-05-29 09:34:17.705</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>1779421637237</v>
+        <v>1780022056058</v>
       </c>
       <c r="C130" t="n">
-        <v>88895</v>
+        <v>84203</v>
       </c>
       <c r="D130" t="n">
-        <v>307.29</v>
+        <v>2242.41</v>
       </c>
       <c r="E130" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="F130" t="n">
-        <v>625</v>
+        <v>4038</v>
       </c>
       <c r="G130" t="n">
-        <v>209.65</v>
+        <v>223.52</v>
       </c>
       <c r="H130" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I130" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J130" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K130" t="n">
+        <v>1645</v>
+      </c>
+      <c r="L130" t="n">
+        <v>109</v>
+      </c>
+      <c r="M130" t="n">
+        <v>1.734</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:15.688</t>
+          <t>2026-05-29 09:34:17.735</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>1779421637439</v>
+        <v>1780022056258</v>
       </c>
       <c r="C131" t="n">
-        <v>88570</v>
+        <v>84283</v>
       </c>
       <c r="D131" t="n">
-        <v>-33.07</v>
+        <v>2210.29</v>
       </c>
       <c r="E131" t="n">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="F131" t="n">
-        <v>966</v>
+        <v>4038</v>
       </c>
       <c r="G131" t="n">
-        <v>213.93</v>
+        <v>223.52</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I131" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J131" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K131" t="n">
+        <v>1475</v>
+      </c>
+      <c r="L131" t="n">
+        <v>112</v>
+      </c>
+      <c r="M131" t="n">
+        <v>1.656</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:15.688</t>
+          <t>2026-05-29 09:34:17.736</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>1779421637640</v>
+        <v>1780022056458</v>
       </c>
       <c r="C132" t="n">
-        <v>88635</v>
+        <v>84509</v>
       </c>
       <c r="D132" t="n">
-        <v>33.58</v>
+        <v>2325.78</v>
       </c>
       <c r="E132" t="n">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="F132" t="n">
-        <v>966</v>
+        <v>4038</v>
       </c>
       <c r="G132" t="n">
-        <v>213.93</v>
+        <v>223.52</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I132" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J132" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K132" t="n">
+        <v>1278</v>
+      </c>
+      <c r="L132" t="n">
+        <v>105</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.754</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:15.689</t>
+          <t>2026-05-29 09:34:17.737</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>1779421637841</v>
+        <v>1780022056658</v>
       </c>
       <c r="C133" t="n">
-        <v>89065</v>
+        <v>84186</v>
       </c>
       <c r="D133" t="n">
-        <v>461.9</v>
+        <v>1886.49</v>
       </c>
       <c r="E133" t="n">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="F133" t="n">
-        <v>966</v>
+        <v>4038</v>
       </c>
       <c r="G133" t="n">
-        <v>213.93</v>
+        <v>223.52</v>
       </c>
       <c r="H133" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I133" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J133" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K133" t="n">
+        <v>1079</v>
+      </c>
+      <c r="L133" t="n">
+        <v>113</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.837</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:16.029</t>
+          <t>2026-05-29 09:34:18.087</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>1779421638043</v>
+        <v>1780022056858</v>
       </c>
       <c r="C134" t="n">
-        <v>88873</v>
+        <v>83858</v>
       </c>
       <c r="D134" t="n">
-        <v>246.81</v>
+        <v>1464.16</v>
       </c>
       <c r="E134" t="n">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="F134" t="n">
-        <v>464</v>
+        <v>4038</v>
       </c>
       <c r="G134" t="n">
-        <v>241.35</v>
+        <v>223.52</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I134" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J134" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K134" t="n">
+        <v>1229</v>
+      </c>
+      <c r="L134" t="n">
+        <v>109</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.8159999999999999</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:16.030</t>
+          <t>2026-05-29 09:34:18.099</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>1779421638244</v>
+        <v>1780022057058</v>
       </c>
       <c r="C135" t="n">
-        <v>89114</v>
+        <v>84199</v>
       </c>
       <c r="D135" t="n">
-        <v>475.47</v>
+        <v>1731.96</v>
       </c>
       <c r="E135" t="n">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="F135" t="n">
-        <v>464</v>
+        <v>4038</v>
       </c>
       <c r="G135" t="n">
-        <v>241.35</v>
+        <v>223.52</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I135" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J135" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K135" t="n">
+        <v>1040</v>
+      </c>
+      <c r="L135" t="n">
+        <v>125</v>
+      </c>
+      <c r="M135" t="n">
+        <v>1.251</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:16.678</t>
+          <t>2026-05-29 09:34:18.123</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>1779421638446</v>
+        <v>1780022057258</v>
       </c>
       <c r="C136" t="n">
-        <v>89343</v>
+        <v>83940</v>
       </c>
       <c r="D136" t="n">
-        <v>680.6900000000001</v>
+        <v>1386.36</v>
       </c>
       <c r="E136" t="n">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="F136" t="n">
-        <v>464</v>
+        <v>1260</v>
       </c>
       <c r="G136" t="n">
-        <v>241.35</v>
+        <v>260.35</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I136" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J136" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K136" t="n">
+        <v>863</v>
+      </c>
+      <c r="L136" t="n">
+        <v>109</v>
+      </c>
+      <c r="M136" t="n">
+        <v>1.834</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:16.679</t>
+          <t>2026-05-29 09:34:20.172</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>1779421638647</v>
+        <v>1780022057458</v>
       </c>
       <c r="C137" t="n">
-        <v>89519</v>
+        <v>83773</v>
       </c>
       <c r="D137" t="n">
-        <v>822.66</v>
+        <v>1150.04</v>
       </c>
       <c r="E137" t="n">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="F137" t="n">
-        <v>464</v>
+        <v>1260</v>
       </c>
       <c r="G137" t="n">
-        <v>241.35</v>
+        <v>260.35</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I137" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J137" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K137" t="n">
+        <v>2713</v>
+      </c>
+      <c r="L137" t="n">
+        <v>110</v>
+      </c>
+      <c r="M137" t="n">
+        <v>1.399</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:16.679</t>
+          <t>2026-05-29 09:34:20.184</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>1779421638848</v>
+        <v>1780022057658</v>
       </c>
       <c r="C138" t="n">
-        <v>89079</v>
+        <v>84102</v>
       </c>
       <c r="D138" t="n">
-        <v>341.53</v>
+        <v>1421.54</v>
       </c>
       <c r="E138" t="n">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="F138" t="n">
-        <v>464</v>
+        <v>1260</v>
       </c>
       <c r="G138" t="n">
-        <v>241.35</v>
+        <v>260.35</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I138" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J138" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K138" t="n">
+        <v>2525</v>
+      </c>
+      <c r="L138" t="n">
+        <v>112</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:17.038</t>
+          <t>2026-05-29 09:34:20.927</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>1779421639050</v>
+        <v>1780022057877</v>
       </c>
       <c r="C139" t="n">
-        <v>89372</v>
+        <v>84019</v>
       </c>
       <c r="D139" t="n">
-        <v>617.45</v>
+        <v>1267.46</v>
       </c>
       <c r="E139" t="n">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="F139" t="n">
-        <v>464</v>
+        <v>580</v>
       </c>
       <c r="G139" t="n">
-        <v>241.35</v>
+        <v>259.5</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I139" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J139" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K139" t="n">
+        <v>3049</v>
+      </c>
+      <c r="L139" t="n">
+        <v>111</v>
+      </c>
+      <c r="M139" t="n">
+        <v>1.393</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:17.038</t>
+          <t>2026-05-29 09:34:20.930</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>1779421639251</v>
+        <v>1780022058077</v>
       </c>
       <c r="C140" t="n">
-        <v>89457</v>
+        <v>83352</v>
       </c>
       <c r="D140" t="n">
-        <v>671.58</v>
+        <v>537.09</v>
       </c>
       <c r="E140" t="n">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="F140" t="n">
-        <v>1289</v>
+        <v>580</v>
       </c>
       <c r="G140" t="n">
-        <v>286.1</v>
+        <v>259.5</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I140" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J140" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K140" t="n">
+        <v>2852</v>
+      </c>
+      <c r="L140" t="n">
+        <v>104</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.9340000000000001</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:17.466</t>
+          <t>2026-05-29 09:34:20.932</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>1779421639453</v>
+        <v>1780022058277</v>
       </c>
       <c r="C141" t="n">
-        <v>88924</v>
+        <v>83412</v>
       </c>
       <c r="D141" t="n">
-        <v>105</v>
+        <v>570.23</v>
       </c>
       <c r="E141" t="n">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="F141" t="n">
-        <v>1289</v>
+        <v>580</v>
       </c>
       <c r="G141" t="n">
-        <v>286.1</v>
+        <v>259.5</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I141" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J141" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K141" t="n">
+        <v>2654</v>
+      </c>
+      <c r="L141" t="n">
+        <v>107</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.872</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:17.467</t>
+          <t>2026-05-29 09:34:20.942</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>1779421639654</v>
+        <v>1780022058477</v>
       </c>
       <c r="C142" t="n">
-        <v>89259</v>
+        <v>83566</v>
       </c>
       <c r="D142" t="n">
-        <v>434.75</v>
+        <v>695.72</v>
       </c>
       <c r="E142" t="n">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="F142" t="n">
-        <v>1289</v>
+        <v>580</v>
       </c>
       <c r="G142" t="n">
-        <v>286.1</v>
+        <v>259.5</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I142" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J142" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K142" t="n">
+        <v>2464</v>
+      </c>
+      <c r="L142" t="n">
+        <v>104</v>
+      </c>
+      <c r="M142" t="n">
+        <v>1.061</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:17.862</t>
+          <t>2026-05-29 09:34:21.045</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>1779421639855</v>
+        <v>1780022058677</v>
       </c>
       <c r="C143" t="n">
-        <v>89389</v>
+        <v>83699</v>
       </c>
       <c r="D143" t="n">
-        <v>543.01</v>
+        <v>793.9400000000001</v>
       </c>
       <c r="E143" t="n">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="F143" t="n">
-        <v>704</v>
+        <v>580</v>
       </c>
       <c r="G143" t="n">
-        <v>288.06</v>
+        <v>259.5</v>
       </c>
       <c r="H143" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I143" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J143" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K143" t="n">
+        <v>2367</v>
+      </c>
+      <c r="L143" t="n">
+        <v>106</v>
+      </c>
+      <c r="M143" t="n">
+        <v>1.151</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:17.862</t>
+          <t>2026-05-29 09:34:21.697</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>1779421640057</v>
+        <v>1780022058877</v>
       </c>
       <c r="C144" t="n">
-        <v>88916</v>
+        <v>83504</v>
       </c>
       <c r="D144" t="n">
-        <v>42.86</v>
+        <v>559.24</v>
       </c>
       <c r="E144" t="n">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="F144" t="n">
-        <v>704</v>
+        <v>959</v>
       </c>
       <c r="G144" t="n">
-        <v>288.06</v>
+        <v>262</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I144" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J144" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K144" t="n">
+        <v>2818</v>
+      </c>
+      <c r="L144" t="n">
+        <v>108</v>
+      </c>
+      <c r="M144" t="n">
+        <v>1.5</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:18.390</t>
+          <t>2026-05-29 09:34:21.698</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>1779421640258</v>
+        <v>1780022059077</v>
       </c>
       <c r="C145" t="n">
-        <v>89235</v>
+        <v>82885</v>
       </c>
       <c r="D145" t="n">
-        <v>359.72</v>
+        <v>-87.72</v>
       </c>
       <c r="E145" t="n">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="F145" t="n">
-        <v>704</v>
+        <v>959</v>
       </c>
       <c r="G145" t="n">
-        <v>288.06</v>
+        <v>262</v>
       </c>
       <c r="H145" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I145" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J145" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K145" t="n">
+        <v>2620</v>
+      </c>
+      <c r="L145" t="n">
+        <v>110</v>
+      </c>
+      <c r="M145" t="n">
+        <v>1.01</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:18.391</t>
+          <t>2026-05-29 09:34:21.700</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>1779421640460</v>
+        <v>1780022059277</v>
       </c>
       <c r="C146" t="n">
-        <v>89506</v>
+        <v>82747</v>
       </c>
       <c r="D146" t="n">
-        <v>612.73</v>
+        <v>-221.34</v>
       </c>
       <c r="E146" t="n">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="F146" t="n">
-        <v>704</v>
+        <v>959</v>
       </c>
       <c r="G146" t="n">
-        <v>288.06</v>
+        <v>262</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I146" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J146" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K146" t="n">
+        <v>2422</v>
+      </c>
+      <c r="L146" t="n">
+        <v>108</v>
+      </c>
+      <c r="M146" t="n">
+        <v>1.325</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:19.094</t>
+          <t>2026-05-29 09:34:21.701</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>1779421640661</v>
+        <v>1780022059739</v>
       </c>
       <c r="C147" t="n">
-        <v>89804</v>
+        <v>83239</v>
       </c>
       <c r="D147" t="n">
-        <v>880.1</v>
+        <v>281.73</v>
       </c>
       <c r="E147" t="n">
-        <v>89</v>
+        <v>68</v>
       </c>
       <c r="F147" t="n">
-        <v>625</v>
+        <v>959</v>
       </c>
       <c r="G147" t="n">
-        <v>296.4</v>
+        <v>262</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I147" t="n">
+        <v>43.62</v>
+      </c>
+      <c r="J147" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K147" t="n">
+        <v>1961</v>
+      </c>
+      <c r="L147" t="n">
+        <v>114</v>
+      </c>
+      <c r="M147" t="n">
+        <v>0.973</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:19.095</t>
+          <t>2026-05-29 09:34:21.702</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>1779421640862</v>
+        <v>1780022059957</v>
       </c>
       <c r="C148" t="n">
-        <v>89487</v>
+        <v>83735</v>
       </c>
       <c r="D148" t="n">
-        <v>519.09</v>
+        <v>763.64</v>
       </c>
       <c r="E148" t="n">
-        <v>89</v>
+        <v>68</v>
       </c>
       <c r="F148" t="n">
-        <v>625</v>
+        <v>959</v>
       </c>
       <c r="G148" t="n">
-        <v>296.4</v>
+        <v>262</v>
       </c>
       <c r="H148" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I148" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J148" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K148" t="n">
+        <v>1744</v>
+      </c>
+      <c r="L148" t="n">
+        <v>106</v>
+      </c>
+      <c r="M148" t="n">
+        <v>0.999</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:19.095</t>
+          <t>2026-05-29 09:34:21.703</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>1779421641064</v>
+        <v>1780022060176</v>
       </c>
       <c r="C149" t="n">
-        <v>89695</v>
+        <v>83394</v>
       </c>
       <c r="D149" t="n">
-        <v>701.14</v>
+        <v>384.46</v>
       </c>
       <c r="E149" t="n">
-        <v>89</v>
+        <v>65</v>
       </c>
       <c r="F149" t="n">
-        <v>625</v>
+        <v>1220</v>
       </c>
       <c r="G149" t="n">
-        <v>296.4</v>
+        <v>276.67</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I149" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J149" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K149" t="n">
+        <v>1526</v>
+      </c>
+      <c r="L149" t="n">
+        <v>109</v>
+      </c>
+      <c r="M149" t="n">
+        <v>0.913</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:19.096</t>
+          <t>2026-05-29 09:34:22.059</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>1779421641265</v>
+        <v>1780022060376</v>
       </c>
       <c r="C150" t="n">
-        <v>90105</v>
+        <v>83235</v>
       </c>
       <c r="D150" t="n">
-        <v>1076.08</v>
+        <v>206.24</v>
       </c>
       <c r="E150" t="n">
-        <v>89</v>
+        <v>65</v>
       </c>
       <c r="F150" t="n">
-        <v>625</v>
+        <v>1220</v>
       </c>
       <c r="G150" t="n">
-        <v>296.4</v>
+        <v>276.67</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I150" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J150" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K150" t="n">
+        <v>1681</v>
+      </c>
+      <c r="L150" t="n">
+        <v>108</v>
+      </c>
+      <c r="M150" t="n">
+        <v>1.598</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:19.497</t>
+          <t>2026-05-29 09:34:22.062</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>1779421641466</v>
+        <v>1780022060576</v>
       </c>
       <c r="C151" t="n">
-        <v>89597</v>
+        <v>83352</v>
       </c>
       <c r="D151" t="n">
-        <v>514.28</v>
+        <v>312.93</v>
       </c>
       <c r="E151" t="n">
-        <v>89</v>
+        <v>65</v>
       </c>
       <c r="F151" t="n">
-        <v>625</v>
+        <v>1220</v>
       </c>
       <c r="G151" t="n">
-        <v>296.4</v>
+        <v>276.67</v>
       </c>
       <c r="H151" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I151" t="n">
+        <v>49.28</v>
+      </c>
+      <c r="J151" t="n">
+        <v>35.46</v>
+      </c>
+      <c r="K151" t="n">
+        <v>1484</v>
+      </c>
+      <c r="L151" t="n">
+        <v>111</v>
+      </c>
+      <c r="M151" t="n">
+        <v>1.608</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:19.498</t>
+          <t>2026-05-29 09:34:22.063</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>1779421641668</v>
+        <v>1780022060776</v>
       </c>
       <c r="C152" t="n">
-        <v>89637</v>
+        <v>82766</v>
       </c>
       <c r="D152" t="n">
-        <v>528.5599999999999</v>
+        <v>-288.72</v>
       </c>
       <c r="E152" t="n">
-        <v>89</v>
+        <v>65</v>
       </c>
       <c r="F152" t="n">
-        <v>625</v>
+        <v>1220</v>
       </c>
       <c r="G152" t="n">
-        <v>296.4</v>
+        <v>276.67</v>
       </c>
       <c r="H152" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I152" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J152" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K152" t="n">
+        <v>1286</v>
+      </c>
+      <c r="L152" t="n">
+        <v>116</v>
+      </c>
+      <c r="M152" t="n">
+        <v>1.147</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:20.075</t>
+          <t>2026-05-29 09:34:22.067</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>1779421641869</v>
+        <v>1780022060976</v>
       </c>
       <c r="C153" t="n">
-        <v>89690</v>
+        <v>82987</v>
       </c>
       <c r="D153" t="n">
-        <v>555.13</v>
+        <v>-53.28</v>
       </c>
       <c r="E153" t="n">
-        <v>89</v>
+        <v>65</v>
       </c>
       <c r="F153" t="n">
-        <v>625</v>
+        <v>1220</v>
       </c>
       <c r="G153" t="n">
-        <v>296.4</v>
+        <v>276.67</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I153" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J153" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K153" t="n">
+        <v>1089</v>
+      </c>
+      <c r="L153" t="n">
+        <v>114</v>
+      </c>
+      <c r="M153" t="n">
+        <v>1.271</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:20.075</t>
+          <t>2026-05-29 09:34:22.875</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>1779421642071</v>
+        <v>1780022061176</v>
       </c>
       <c r="C154" t="n">
-        <v>89811</v>
+        <v>82818</v>
       </c>
       <c r="D154" t="n">
-        <v>648.38</v>
+        <v>-219.62</v>
       </c>
       <c r="E154" t="n">
-        <v>89</v>
+        <v>65</v>
       </c>
       <c r="F154" t="n">
-        <v>625</v>
+        <v>1220</v>
       </c>
       <c r="G154" t="n">
-        <v>296.4</v>
+        <v>276.67</v>
       </c>
       <c r="H154" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I154" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J154" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K154" t="n">
+        <v>1698</v>
+      </c>
+      <c r="L154" t="n">
+        <v>108</v>
+      </c>
+      <c r="M154" t="n">
+        <v>1.292</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:20.452</t>
+          <t>2026-05-29 09:34:22.878</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>1779421642272</v>
+        <v>1780022061376</v>
       </c>
       <c r="C155" t="n">
-        <v>89181</v>
+        <v>81815</v>
       </c>
       <c r="D155" t="n">
-        <v>-14.04</v>
+        <v>-1211.64</v>
       </c>
       <c r="E155" t="n">
-        <v>89</v>
+        <v>65</v>
       </c>
       <c r="F155" t="n">
-        <v>1631</v>
+        <v>1220</v>
       </c>
       <c r="G155" t="n">
-        <v>296.4</v>
+        <v>276.67</v>
       </c>
       <c r="H155" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I155" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J155" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K155" t="n">
+        <v>1501</v>
+      </c>
+      <c r="L155" t="n">
+        <v>114</v>
+      </c>
+      <c r="M155" t="n">
+        <v>1.388</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:34:22.881</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>1780022061576</v>
+      </c>
+      <c r="C156" t="n">
+        <v>81503</v>
+      </c>
+      <c r="D156" t="n">
+        <v>-1463.06</v>
+      </c>
+      <c r="E156" t="n">
+        <v>65</v>
+      </c>
+      <c r="F156" t="n">
+        <v>1220</v>
+      </c>
+      <c r="G156" t="n">
+        <v>276.67</v>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I156" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J156" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K156" t="n">
+        <v>1304</v>
+      </c>
+      <c r="L156" t="n">
+        <v>114</v>
+      </c>
+      <c r="M156" t="n">
+        <v>0.9389999999999999</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:34:22.883</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>1780022061776</v>
+      </c>
+      <c r="C157" t="n">
+        <v>82336</v>
+      </c>
+      <c r="D157" t="n">
+        <v>-556.9</v>
+      </c>
+      <c r="E157" t="n">
+        <v>65</v>
+      </c>
+      <c r="F157" t="n">
+        <v>1220</v>
+      </c>
+      <c r="G157" t="n">
+        <v>276.67</v>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I157" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J157" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K157" t="n">
+        <v>1106</v>
+      </c>
+      <c r="L157" t="n">
+        <v>116</v>
+      </c>
+      <c r="M157" t="n">
+        <v>1.461</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:34:23.461</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>1780022061976</v>
+      </c>
+      <c r="C158" t="n">
+        <v>82295</v>
+      </c>
+      <c r="D158" t="n">
+        <v>-570.0599999999999</v>
+      </c>
+      <c r="E158" t="n">
+        <v>65</v>
+      </c>
+      <c r="F158" t="n">
+        <v>1220</v>
+      </c>
+      <c r="G158" t="n">
+        <v>276.67</v>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I158" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J158" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K158" t="n">
+        <v>1484</v>
+      </c>
+      <c r="L158" t="n">
+        <v>110</v>
+      </c>
+      <c r="M158" t="n">
+        <v>0.83</v>
       </c>
     </row>
   </sheetData>
